--- a/Plantilla_Cotizacion_Manual_RA.xlsx
+++ b/Plantilla_Cotizacion_Manual_RA.xlsx
@@ -4,46 +4,49 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Cotización RA" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="Cotización" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Cotización RA'!$A1:$G55</definedName>
-  </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="58">
   <si>
     <t>ACR Networks &amp; Solutions, SRL</t>
   </si>
   <si>
-    <t>[{"text":"RNC ","font":{"name":"Calibri","size":8,"color":{"argb":"FF94A3B8"},"bold":true}},{"text":"1-32-12345-6","font":{"name":"Calibri","size":9.5,"color":{"argb":"FF0F172A"},"bold":true}}]</t>
+    <t>[{"text":"RNC  ","font":{"name":"Calibri","size":8,"bold":true,"color":{"argb":"FF94A3B8"}}},{"text":"1-32-12345-6","font":{"name":"Calibri","size":10,"bold":true,"color":{"argb":"FF0F172A"}}}]</t>
   </si>
   <si>
     <t>ACR NETWORKS &amp; SOLUTIONS</t>
   </si>
   <si>
-    <t>Santo Domingo, República Dominicana</t>
+    <t>Av. Winston Churchill #95, Edificio Acrópolis, Piantini, Santo Domingo, R.D.</t>
   </si>
   <si>
     <t>Infraestructura de Redes · Seguridad Electrónica · Fibra Óptica</t>
   </si>
   <si>
-    <t>Tel +1 809 000 0000  ·  contacto@acrnetworks.do  ·  https://acrnetworks.do</t>
+    <t>Tel. (809) 547-2828  ·  ventas@acrnetworks.do</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>https://acrnetworks.do</t>
   </si>
   <si>
     <t>COTIZACIÓN</t>
   </si>
   <si>
-    <t>COT-MANUAL-001</t>
-  </si>
-  <si>
-    <t>Plantilla Manual · Edición Offline</t>
-  </si>
-  <si>
-    <t>[{"text":"Emisión: ","font":{"name":"Calibri","size":8,"color":{"argb":"FF94A3B8"},"bold":true}},{"text":"2026-05-22","font":{"name":"Calibri","size":8.5,"color":{"argb":"FF0F172A"},"bold":true}},{"text":"  ·  Válida hasta: ","font":{"name":"Calibri","size":8,"color":{"argb":"FF94A3B8"},"bold":true}},{"text":"2026-06-21","font":{"name":"Calibri","size":8.5,"color":{"argb":"FF0F172A"},"bold":true}}]</t>
+    <t>COT-2026-0521-001</t>
+  </si>
+  <si>
+    <t>Documento Electrónico Verificable</t>
+  </si>
+  <si>
+    <t>[{"text":"Emisión: ","font":{"name":"Calibri","size":8,"color":{"argb":"FF94A3B8"},"bold":true}},{"text":"2026-05-22","font":{"name":"Calibri","size":8.5,"color":{"argb":"FF0F172A"},"bold":true}},{"text":"   ·   Válida hasta: ","font":{"name":"Calibri","size":8,"color":{"argb":"FF94A3B8"},"bold":true}},{"text":"2026-06-21","font":{"name":"Calibri","size":8.5,"color":{"argb":"FF0F172A"},"bold":true}}]</t>
   </si>
   <si>
     <t>CLIENTE</t>
@@ -52,25 +55,40 @@
     <t>Razón Social</t>
   </si>
   <si>
-    <t>RNC</t>
+    <t>RNC / Contacto</t>
   </si>
   <si>
     <t>Dirección</t>
   </si>
   <si>
-    <t/>
+    <t>TechSolutions Caribe, SRL</t>
+  </si>
+  <si>
+    <t>1-30-50128-3</t>
+  </si>
+  <si>
+    <t>Av. 27 de Febrero #500, Ensanche Naco, Santo Domingo, R.D.</t>
+  </si>
+  <si>
+    <t>Cliente #: CLI-2026-00128  ·  Ing. Luis Martínez</t>
+  </si>
+  <si>
+    <t>Tel. (809) 555-1234</t>
+  </si>
+  <si>
+    <t>compras@techsolutions.com.do</t>
   </si>
   <si>
     <t>DETALLE DE PRODUCTOS Y SERVICIOS</t>
   </si>
   <si>
-    <t>Ítems</t>
-  </si>
-  <si>
-    <t>Código / Modelo</t>
-  </si>
-  <si>
-    <t>Descripción Técnica</t>
+    <t>#</t>
+  </si>
+  <si>
+    <t>Código</t>
+  </si>
+  <si>
+    <t>Descripción</t>
   </si>
   <si>
     <t>Cant.</t>
@@ -85,49 +103,352 @@
     <t>Importe (RD$)</t>
   </si>
   <si>
+    <t>MKT-RB5009</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF0F172A"/>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Router MikroTik RB5009UG+S+IN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF64748B"/>
+        <sz val="8.5"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>CPU 4-core ARM, 9× Gigabit, 1× SFP+ 10G, RouterOS L5</t>
+    </r>
+  </si>
+  <si>
+    <t>FO-SM-1KM</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF0F172A"/>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Cable de Fibra Óptica Single-Mode 9/125µm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF64748B"/>
+        <sz val="8.5"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Armado, exterior, anti-roedor — rollo 1000 m</t>
+    </r>
+  </si>
+  <si>
+    <t>SC-APC-50</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF0F172A"/>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Conectores SC/APC Pre-pulidos</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF64748B"/>
+        <sz val="8.5"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Conector mecánico, pérdida &lt;0.3 dB</t>
+    </r>
+  </si>
+  <si>
+    <t>HIK-DS-4MP</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF0F172A"/>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Cámara IP HIKVISION 4MP DS-2CD2143G2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF64748B"/>
+        <sz val="8.5"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Bullet, IR 30m, PoE, lente 2.8mm, IP67</t>
+    </r>
+  </si>
+  <si>
+    <t>HIK-NVR16</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF0F172A"/>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>NVR HIKVISION DS-7616NI-K2/16P</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF64748B"/>
+        <sz val="8.5"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>16 canales, 16 puertos PoE, H.265+, 2 bahías HDD</t>
+    </r>
+  </si>
+  <si>
+    <t>HDD-WD-6TB</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF0F172A"/>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Disco Duro WD Purple 6TB Surveillance</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF64748B"/>
+        <sz val="8.5"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>24/7, 256 MB caché, SATA III</t>
+    </r>
+  </si>
+  <si>
+    <t>UPS-APC15K</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF0F172A"/>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>UPS APC Smart-UPS 1500VA Line-Interactive</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF64748B"/>
+        <sz val="8.5"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Salidas IEC, batería sellada, software PowerChute</t>
+    </r>
+  </si>
+  <si>
+    <t>INST-CCTV</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF0F172A"/>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Servicio de Instalación y Configuración CCTV</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF64748B"/>
+        <sz val="8.5"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Tendido cableado UTP Cat6, configuración NVR, capacitación</t>
+    </r>
+  </si>
+  <si>
     <t>Subtotal</t>
   </si>
   <si>
     <t>Total Neto</t>
   </si>
   <si>
-    <t>CONDICIONES GENERALES</t>
-  </si>
-  <si>
-    <t>·  Esta cotización tiene carácter informativo y no constituye documento fiscal.</t>
-  </si>
-  <si>
-    <t>·  Los precios pueden estar sujetos a cambio sin previo aviso fuera del período de validez (30 días desde la emisión).</t>
-  </si>
-  <si>
-    <t>·  Para emisión de factura formal se requiere confirmación por escrito.</t>
-  </si>
-  <si>
-    <t>·  Tiempo de entrega: a confirmar contra disponibilidad de stock al momento de la orden de compra.</t>
-  </si>
-  <si>
-    <t>·  Forma de pago: 50% al confirmar la orden / 50% contra entrega — salvo acuerdo distinto por escrito.</t>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF64748B"/>
+        <sz val="7.5"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">Validez
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF0F172A"/>
+        <sz val="9"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>30 días desde la emisión</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF64748B"/>
+        <sz val="7.5"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">Forma de Pago
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF0F172A"/>
+        <sz val="9"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>50% confirmación · 50% contra entrega</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF64748B"/>
+        <sz val="7.5"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">Tiempo Entrega
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF0F172A"/>
+        <sz val="9"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>7-10 días laborables</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF64748B"/>
+        <sz val="7.5"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">Garantía
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF0F172A"/>
+        <sz val="9"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>12 meses · defectos de fábrica</t>
+    </r>
+  </si>
+  <si>
+    <t>NOTAS DEL PROYECTO</t>
+  </si>
+  <si>
+    <t>Proyecto: Instalación de sistema CCTV de 8 cámaras IP + tendido de fibra óptica punto a punto entre las dos sedes del cliente. La instalación incluye configuración del NVR, integración con red existente del cliente y capacitación básica al personal de TI. Garantía sobre defectos de fábrica únicamente — no cubre daños por descargas eléctricas, manipulación incorrecta ni eventos atmosféricos.</t>
   </si>
   <si>
     <t>ACEPTACIÓN DEL CLIENTE</t>
   </si>
   <si>
+    <t>CRISTIAN ROSARIO</t>
+  </si>
+  <si>
     <t>Firma · Sello · Fecha</t>
   </si>
   <si>
-    <t>Representante Autorizado · Firma · Sello</t>
-  </si>
-  <si>
-    <t>ANEXO FOTOGRÁFICO</t>
-  </si>
-  <si>
-    <t>Insertar fotografías del levantamiento · Cuadrícula 2×2 simétrica</t>
-  </si>
-  <si>
-    <t>[ FOTO ]</t>
-  </si>
-  <si>
-    <t>Pie de foto / ubicación</t>
+    <t>Gerente de Operaciones · ACR Networks &amp; Solutions, SRL</t>
   </si>
 </sst>
 </file>
@@ -138,7 +459,7 @@
     <numFmt numFmtId="164" formatCode="00"/>
     <numFmt numFmtId="165" formatCode="&quot;RD$&quot; #,##0.00"/>
   </numFmts>
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="29" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -171,20 +492,31 @@
     </font>
     <font>
       <color rgb="FF64748B"/>
-      <sz val="7.5"/>
+      <sz val="8"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF1E40AF"/>
+      <sz val="8"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FF1E293B"/>
-      <sz val="14"/>
+      <sz val="16"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FF0F172A"/>
-      <sz val="14"/>
+      <sz val="15"/>
       <name val="Consolas"/>
+    </font>
+    <font>
+      <color rgb="FF64748B"/>
+      <sz val="7.5"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
@@ -201,7 +533,23 @@
     <font>
       <b/>
       <color rgb="FF0F172A"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF0F172A"/>
       <sz val="10"/>
+      <name val="Consolas"/>
+    </font>
+    <font>
+      <color rgb="FF1E293B"/>
+      <sz val="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF475569"/>
+      <sz val="8.5"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -218,17 +566,12 @@
     <font>
       <b/>
       <color rgb="FF1E293B"/>
-      <sz val="8"/>
+      <sz val="8.5"/>
       <name val="Consolas"/>
     </font>
     <font>
       <color rgb="FF0F172A"/>
       <sz val="9.5"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <color rgb="FF0F172A"/>
-      <sz val="9"/>
       <name val="Consolas"/>
     </font>
     <font>
@@ -243,9 +586,14 @@
       <name val="Consolas"/>
     </font>
     <font>
+      <color rgb="FFCBD5E1"/>
+      <sz val="8"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <b/>
       <color rgb="FF475569"/>
-      <sz val="8"/>
+      <sz val="8.5"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -261,14 +609,8 @@
       <name val="Consolas"/>
     </font>
     <font>
-      <b/>
       <color rgb="FF334155"/>
-      <sz val="7.5"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <color rgb="FF475569"/>
-      <sz val="7.5"/>
+      <sz val="9"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -280,18 +622,6 @@
     <font>
       <color rgb="FF64748B"/>
       <sz val="7"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF334155"/>
-      <sz val="9"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF94A3B8"/>
-      <sz val="9"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -318,7 +648,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -365,9 +695,7 @@
       <top style="thin">
         <color rgb="FFE2E8F0"/>
       </top>
-      <bottom style="hair">
-        <color rgb="FFE2E8F0"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -377,9 +705,18 @@
       <right style="thin">
         <color rgb="FFE2E8F0"/>
       </right>
-      <top style="hair">
-        <color rgb="FFE2E8F0"/>
-      </top>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE2E8F0"/>
+      </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FFE2E8F0"/>
       </bottom>
@@ -426,6 +763,56 @@
         <color rgb="FF94A3B8"/>
       </top>
       <bottom style="hair">
+        <color rgb="FFE2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFE2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF1E40AF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFE2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFE2E8F0"/>
+      </right>
+      <top/>
+      <bottom style="thin">
         <color rgb="FFE2E8F0"/>
       </bottom>
       <diagonal/>
@@ -439,154 +826,149 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="dashed">
-        <color rgb="FFCBD5E1"/>
-      </left>
-      <right style="dashed">
-        <color rgb="FFCBD5E1"/>
-      </right>
-      <top style="dashed">
-        <color rgb="FFCBD5E1"/>
-      </top>
-      <bottom style="dashed">
-        <color rgb="FFCBD5E1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="3" fontId="15" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="19" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="15" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="19" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="4" fontId="16" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="20" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="4" fontId="17" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="21" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="17" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="3" fontId="15" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="19" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="15" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="19" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="4" fontId="16" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="20" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="4" fontId="17" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="21" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="25" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -608,14 +990,14 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor editAs="absolute">
+  <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>105000</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>5000</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>18000</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="5143500" cy="1333500"/>
+    <xdr:ext cx="666750" cy="666750"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="1" name="Picture 1">
@@ -631,6 +1013,45 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>140000</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="5143500" cy="1333500"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -976,15 +1397,15 @@
     <tabColor rgb="FF1E40AF"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="44" customWidth="1"/>
-    <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="4" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -996,110 +1417,104 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
     </row>
-    <row r="2" ht="26" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="2" ht="18" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2"/>
       <c r="C2" s="2"/>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2"/>
+      <c r="E2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+    <row r="3" ht="14" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4"/>
       <c r="C3" s="4"/>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4"/>
+      <c r="E3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="5"/>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
     </row>
-    <row r="4" ht="14" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+    <row r="4" ht="14" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="6"/>
       <c r="C4" s="6"/>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="6"/>
+      <c r="E4" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="7"/>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
     </row>
-    <row r="5" ht="3" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
+    <row r="5" ht="14" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5"/>
+      <c r="D5"/>
+      <c r="E5" s="8" t="s">
+        <v>7</v>
+      </c>
       <c r="F5" s="8"/>
       <c r="G5" s="8"/>
     </row>
-    <row r="6" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
-        <v>6</v>
-      </c>
+    <row r="6" ht="3" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="9"/>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
-      <c r="D6" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-    </row>
-    <row r="7" ht="16" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+    </row>
+    <row r="7" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="12" t="s">
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
-    </row>
-    <row r="8" ht="10" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9" ht="14" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+    </row>
+    <row r="8" ht="16" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-    </row>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
+    </row>
+    <row r="9" ht="10" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="10" ht="14" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10" s="14"/>
       <c r="C10" s="14"/>
-      <c r="D10" s="14" t="s">
-        <v>12</v>
-      </c>
+      <c r="D10" s="14"/>
       <c r="E10" s="14"/>
-      <c r="F10" s="14" t="s">
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+    </row>
+    <row r="11" ht="14" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="15" t="s">
         <v>13</v>
-      </c>
-      <c r="G10" s="14"/>
-    </row>
-    <row r="11" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="15" t="s">
-        <v>14</v>
       </c>
       <c r="B11" s="15"/>
       <c r="C11" s="15"/>
@@ -1108,616 +1523,478 @@
       </c>
       <c r="E11" s="15"/>
       <c r="F11" s="15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G11" s="15"/>
     </row>
-    <row r="12" ht="14" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" ht="14" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-    </row>
-    <row r="14" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
+    <row r="12" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="E12" s="17"/>
+      <c r="F12" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="G12" s="18"/>
+    </row>
+    <row r="13" ht="16" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="F14" s="18" t="s">
+      <c r="E13" s="19"/>
+      <c r="F13" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="G14" s="18" t="s">
+      <c r="G13" s="19"/>
+    </row>
+    <row r="14" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" ht="14" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="14" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="15" ht="21" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="19">
+      <c r="B15" s="14"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+    </row>
+    <row r="16" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="G16" s="22" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="23">
         <v>1</v>
       </c>
-      <c r="B15" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="D15" s="22"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="24">
-        <f>IFERROR(D15*E15*0.18,0)</f>
-        <v>0</v>
-      </c>
-      <c r="G15" s="25">
-        <f>IFERROR(D15*E15,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" ht="21" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="26">
+      <c r="B17" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" s="26">
+        <v>1</v>
+      </c>
+      <c r="E17" s="27">
+        <v>24500</v>
+      </c>
+      <c r="F17" s="28">
+        <f>IFERROR(D17*E17*0.18,0)</f>
+        <v>4410</v>
+      </c>
+      <c r="G17" s="29">
+        <f>IFERROR(D17*E17,0)</f>
+        <v>24500</v>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="30">
         <v>2</v>
       </c>
-      <c r="B16" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="C16" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="D16" s="29"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="31">
-        <f>IFERROR(D16*E16*0.18,0)</f>
-        <v>0</v>
-      </c>
-      <c r="G16" s="32">
-        <f>IFERROR(D16*E16,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" ht="21" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="19">
+      <c r="B18" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" s="33">
+        <v>1500</v>
+      </c>
+      <c r="E18" s="34">
+        <v>78</v>
+      </c>
+      <c r="F18" s="35">
+        <f>IFERROR(D18*E18*0.18,0)</f>
+        <v>21060</v>
+      </c>
+      <c r="G18" s="36">
+        <f>IFERROR(D18*E18,0)</f>
+        <v>117000</v>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="23">
         <v>3</v>
       </c>
-      <c r="B17" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="C17" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="D17" s="22"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="24">
-        <f>IFERROR(D17*E17*0.18,0)</f>
-        <v>0</v>
-      </c>
-      <c r="G17" s="25">
-        <f>IFERROR(D17*E17,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" ht="21" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="26">
+      <c r="B19" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" s="26">
+        <v>50</v>
+      </c>
+      <c r="E19" s="27">
+        <v>145</v>
+      </c>
+      <c r="F19" s="28">
+        <f>IFERROR(D19*E19*0.18,0)</f>
+        <v>1305</v>
+      </c>
+      <c r="G19" s="29">
+        <f>IFERROR(D19*E19,0)</f>
+        <v>7250</v>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="30">
         <v>4</v>
       </c>
-      <c r="B18" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="C18" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="D18" s="29"/>
-      <c r="E18" s="30"/>
-      <c r="F18" s="31">
-        <f>IFERROR(D18*E18*0.18,0)</f>
-        <v>0</v>
-      </c>
-      <c r="G18" s="32">
-        <f>IFERROR(D18*E18,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" ht="21" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="19">
+      <c r="B20" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="D20" s="33">
+        <v>8</v>
+      </c>
+      <c r="E20" s="34">
+        <v>6850</v>
+      </c>
+      <c r="F20" s="35">
+        <f>IFERROR(D20*E20*0.18,0)</f>
+        <v>9864</v>
+      </c>
+      <c r="G20" s="36">
+        <f>IFERROR(D20*E20,0)</f>
+        <v>54800</v>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="23">
         <v>5</v>
       </c>
-      <c r="B19" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="C19" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="D19" s="22"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="24">
-        <f>IFERROR(D19*E19*0.18,0)</f>
-        <v>0</v>
-      </c>
-      <c r="G19" s="25">
-        <f>IFERROR(D19*E19,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" ht="21" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="26">
+      <c r="B21" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21" s="26">
+        <v>1</v>
+      </c>
+      <c r="E21" s="27">
+        <v>21500</v>
+      </c>
+      <c r="F21" s="28">
+        <f>IFERROR(D21*E21*0.18,0)</f>
+        <v>3870</v>
+      </c>
+      <c r="G21" s="29">
+        <f>IFERROR(D21*E21,0)</f>
+        <v>21500</v>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="30">
         <v>6</v>
       </c>
-      <c r="B20" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="C20" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="D20" s="29"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="31">
-        <f>IFERROR(D20*E20*0.18,0)</f>
-        <v>0</v>
-      </c>
-      <c r="G20" s="32">
-        <f>IFERROR(D20*E20,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" ht="21" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="19">
+      <c r="B22" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="D22" s="33">
+        <v>2</v>
+      </c>
+      <c r="E22" s="34">
+        <v>7950</v>
+      </c>
+      <c r="F22" s="35">
+        <f>IFERROR(D22*E22*0.18,0)</f>
+        <v>2862</v>
+      </c>
+      <c r="G22" s="36">
+        <f>IFERROR(D22*E22,0)</f>
+        <v>15900</v>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="23">
         <v>7</v>
       </c>
-      <c r="B21" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="C21" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="D21" s="22"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="24">
-        <f>IFERROR(D21*E21*0.18,0)</f>
-        <v>0</v>
-      </c>
-      <c r="G21" s="25">
-        <f>IFERROR(D21*E21,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" ht="21" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="26">
+      <c r="B23" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="D23" s="26">
+        <v>1</v>
+      </c>
+      <c r="E23" s="27">
+        <v>18500</v>
+      </c>
+      <c r="F23" s="28">
+        <f>IFERROR(D23*E23*0.18,0)</f>
+        <v>3330</v>
+      </c>
+      <c r="G23" s="29">
+        <f>IFERROR(D23*E23,0)</f>
+        <v>18500</v>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="30">
         <v>8</v>
       </c>
-      <c r="B22" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="C22" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="D22" s="29"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="31">
-        <f>IFERROR(D22*E22*0.18,0)</f>
-        <v>0</v>
-      </c>
-      <c r="G22" s="32">
-        <f>IFERROR(D22*E22,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" ht="21" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="19">
+      <c r="B24" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="C24" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="D24" s="33">
+        <v>1</v>
+      </c>
+      <c r="E24" s="34">
+        <v>35000</v>
+      </c>
+      <c r="F24" s="35">
+        <f>IFERROR(D24*E24*0.18,0)</f>
+        <v>6300</v>
+      </c>
+      <c r="G24" s="36">
+        <f>IFERROR(D24*E24,0)</f>
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="37">
         <v>9</v>
       </c>
-      <c r="B23" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="C23" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="D23" s="22"/>
-      <c r="E23" s="23"/>
-      <c r="F23" s="24">
-        <f>IFERROR(D23*E23*0.18,0)</f>
-        <v>0</v>
-      </c>
-      <c r="G23" s="25">
-        <f>IFERROR(D23*E23,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" ht="21" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="26">
-        <v>10</v>
-      </c>
-      <c r="B24" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="C24" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="D24" s="29"/>
-      <c r="E24" s="30"/>
-      <c r="F24" s="31">
-        <f>IFERROR(D24*E24*0.18,0)</f>
-        <v>0</v>
-      </c>
-      <c r="G24" s="32">
-        <f>IFERROR(D24*E24,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" ht="21" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="19">
-        <v>11</v>
-      </c>
-      <c r="B25" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="C25" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="D25" s="22"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="24">
+      <c r="B25" s="38"/>
+      <c r="C25" s="38"/>
+      <c r="D25" s="38"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="28">
         <f>IFERROR(D25*E25*0.18,0)</f>
         <v>0</v>
       </c>
-      <c r="G25" s="25">
+      <c r="G25" s="29">
         <f>IFERROR(D25*E25,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="26" ht="21" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="26">
-        <v>12</v>
-      </c>
-      <c r="B26" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="C26" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="D26" s="29"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="31">
+    <row r="26" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="37">
+        <v>10</v>
+      </c>
+      <c r="B26" s="38"/>
+      <c r="C26" s="38"/>
+      <c r="D26" s="38"/>
+      <c r="E26" s="38"/>
+      <c r="F26" s="28">
         <f>IFERROR(D26*E26*0.18,0)</f>
         <v>0</v>
       </c>
-      <c r="G26" s="32">
+      <c r="G26" s="29">
         <f>IFERROR(D26*E26,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="27" ht="21" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="19">
-        <v>13</v>
-      </c>
-      <c r="B27" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="C27" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="D27" s="22"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="24">
+    <row r="27" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="37">
+        <v>11</v>
+      </c>
+      <c r="B27" s="38"/>
+      <c r="C27" s="38"/>
+      <c r="D27" s="38"/>
+      <c r="E27" s="38"/>
+      <c r="F27" s="28">
         <f>IFERROR(D27*E27*0.18,0)</f>
         <v>0</v>
       </c>
-      <c r="G27" s="25">
+      <c r="G27" s="29">
         <f>IFERROR(D27*E27,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="28" ht="21" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="26">
-        <v>14</v>
-      </c>
-      <c r="B28" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="C28" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="D28" s="29"/>
-      <c r="E28" s="30"/>
-      <c r="F28" s="31">
-        <f>IFERROR(D28*E28*0.18,0)</f>
-        <v>0</v>
-      </c>
-      <c r="G28" s="32">
-        <f>IFERROR(D28*E28,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" ht="21" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="19">
-        <v>15</v>
-      </c>
-      <c r="B29" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="C29" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="D29" s="22"/>
-      <c r="E29" s="23"/>
-      <c r="F29" s="24">
-        <f>IFERROR(D29*E29*0.18,0)</f>
-        <v>0</v>
-      </c>
-      <c r="G29" s="25">
-        <f>IFERROR(D29*E29,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" ht="8" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" ht="22" customHeight="1" spans="5:7" x14ac:dyDescent="0.25">
-      <c r="E31" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="F31" s="33"/>
-      <c r="G31" s="34">
-        <f>SUM(G15:G29)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" ht="22" customHeight="1" spans="5:7" x14ac:dyDescent="0.25">
-      <c r="E32" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="F32" s="33"/>
-      <c r="G32" s="34">
-        <f>SUM(F15:F29)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" ht="28" customHeight="1" spans="5:7" x14ac:dyDescent="0.25">
-      <c r="E33" s="35" t="s">
-        <v>24</v>
-      </c>
-      <c r="F33" s="35"/>
-      <c r="G33" s="36">
-        <f>G31+G32</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" ht="14" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="8" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" ht="22" customHeight="1" spans="5:7" x14ac:dyDescent="0.25">
+      <c r="E29" s="39" t="s">
+        <v>46</v>
+      </c>
+      <c r="F29" s="39"/>
+      <c r="G29" s="40">
+        <f>SUM(G17:G27)</f>
+        <v>294450</v>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1" spans="5:7" x14ac:dyDescent="0.25">
+      <c r="E30" s="39" t="s">
+        <v>28</v>
+      </c>
+      <c r="F30" s="39"/>
+      <c r="G30" s="40">
+        <f>SUM(F17:F27)</f>
+        <v>53001</v>
+      </c>
+    </row>
+    <row r="31" ht="28" customHeight="1" spans="5:7" x14ac:dyDescent="0.25">
+      <c r="E31" s="41" t="s">
+        <v>47</v>
+      </c>
+      <c r="F31" s="41"/>
+      <c r="G31" s="42">
+        <f>G29+G30</f>
+        <v>347451</v>
+      </c>
+    </row>
+    <row r="32" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="43" t="s">
+        <v>48</v>
+      </c>
+      <c r="B33" s="43"/>
+      <c r="C33" s="44" t="s">
+        <v>49</v>
+      </c>
+      <c r="D33" s="43" t="s">
+        <v>50</v>
+      </c>
+      <c r="E33" s="43"/>
+      <c r="F33" s="43" t="s">
+        <v>51</v>
+      </c>
+      <c r="G33" s="43"/>
+    </row>
+    <row r="34" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="35" ht="14" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="37" t="s">
-        <v>25</v>
-      </c>
-      <c r="B35" s="37"/>
-      <c r="C35" s="37"/>
-      <c r="D35" s="37"/>
-      <c r="E35" s="37"/>
-      <c r="F35" s="37"/>
-      <c r="G35" s="37"/>
-    </row>
-    <row r="36" ht="14" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="38" t="s">
-        <v>26</v>
-      </c>
-      <c r="B36" s="38"/>
-      <c r="C36" s="38"/>
-      <c r="D36" s="38"/>
-      <c r="E36" s="38"/>
-      <c r="F36" s="38"/>
-      <c r="G36" s="38"/>
-    </row>
-    <row r="37" ht="14" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="38" t="s">
-        <v>27</v>
-      </c>
-      <c r="B37" s="38"/>
-      <c r="C37" s="38"/>
-      <c r="D37" s="38"/>
-      <c r="E37" s="38"/>
-      <c r="F37" s="38"/>
-      <c r="G37" s="38"/>
-    </row>
-    <row r="38" ht="14" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="38" t="s">
-        <v>28</v>
-      </c>
-      <c r="B38" s="38"/>
-      <c r="C38" s="38"/>
-      <c r="D38" s="38"/>
-      <c r="E38" s="38"/>
-      <c r="F38" s="38"/>
-      <c r="G38" s="38"/>
+      <c r="A35" s="45" t="s">
+        <v>52</v>
+      </c>
+      <c r="B35" s="45"/>
+      <c r="C35" s="45"/>
+      <c r="D35" s="45"/>
+      <c r="E35" s="45"/>
+      <c r="F35" s="45"/>
+      <c r="G35" s="45"/>
+    </row>
+    <row r="36" ht="50" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="B36" s="46"/>
+      <c r="C36" s="46"/>
+      <c r="D36" s="46"/>
+      <c r="E36" s="46"/>
+      <c r="F36" s="46"/>
+      <c r="G36" s="46"/>
+    </row>
+    <row r="37" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="44" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="47"/>
+      <c r="B38" s="47"/>
+      <c r="C38" s="47"/>
+      <c r="E38" s="47"/>
+      <c r="F38" s="47"/>
+      <c r="G38" s="47"/>
     </row>
     <row r="39" ht="14" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="B39" s="38"/>
-      <c r="C39" s="38"/>
-      <c r="D39" s="38"/>
-      <c r="E39" s="38"/>
-      <c r="F39" s="38"/>
-      <c r="G39" s="38"/>
-    </row>
-    <row r="40" ht="14" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="B40" s="38"/>
-      <c r="C40" s="38"/>
-      <c r="D40" s="38"/>
-      <c r="E40" s="38"/>
-      <c r="F40" s="38"/>
-      <c r="G40" s="38"/>
-    </row>
-    <row r="41" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" ht="46" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="39"/>
-      <c r="B42" s="39"/>
-      <c r="C42" s="39"/>
-      <c r="E42" s="39"/>
-      <c r="F42" s="39"/>
-      <c r="G42" s="39"/>
-    </row>
-    <row r="43" ht="16" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="40" t="s">
-        <v>31</v>
-      </c>
-      <c r="B43" s="40"/>
-      <c r="C43" s="40"/>
-      <c r="E43" s="40" t="s">
-        <v>0</v>
-      </c>
-      <c r="F43" s="40"/>
-      <c r="G43" s="40"/>
-    </row>
-    <row r="44" ht="13" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="B44" s="41"/>
-      <c r="C44" s="41"/>
-      <c r="E44" s="41" t="s">
-        <v>33</v>
-      </c>
-      <c r="F44" s="41"/>
-      <c r="G44" s="41"/>
-    </row>
-    <row r="47" ht="16" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="B47" s="42"/>
-      <c r="C47" s="42"/>
-      <c r="D47" s="42"/>
-      <c r="E47" s="42"/>
-      <c r="F47" s="42"/>
-      <c r="G47" s="42"/>
-    </row>
-    <row r="48" ht="12" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="43" t="s">
-        <v>35</v>
-      </c>
-      <c r="B48" s="43"/>
-      <c r="C48" s="43"/>
-      <c r="D48" s="43"/>
-      <c r="E48" s="43"/>
-      <c r="F48" s="43"/>
-      <c r="G48" s="43"/>
-    </row>
-    <row r="49" ht="90" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="B49" s="44"/>
-      <c r="C49" s="44"/>
-      <c r="E49" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="F49" s="44"/>
-      <c r="G49" s="44"/>
-    </row>
-    <row r="50" ht="12" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="45" t="s">
-        <v>37</v>
-      </c>
-      <c r="B50" s="45"/>
-      <c r="C50" s="45"/>
-      <c r="E50" s="45" t="s">
-        <v>37</v>
-      </c>
-      <c r="F50" s="45"/>
-      <c r="G50" s="45"/>
-    </row>
-    <row r="51" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" ht="90" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="B52" s="44"/>
-      <c r="C52" s="44"/>
-      <c r="E52" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="F52" s="44"/>
-      <c r="G52" s="44"/>
-    </row>
-    <row r="53" ht="12" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="45" t="s">
-        <v>37</v>
-      </c>
-      <c r="B53" s="45"/>
-      <c r="C53" s="45"/>
-      <c r="E53" s="45" t="s">
-        <v>37</v>
-      </c>
-      <c r="F53" s="45"/>
-      <c r="G53" s="45"/>
-    </row>
-    <row r="54" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="A39" s="48" t="s">
+        <v>54</v>
+      </c>
+      <c r="B39" s="48"/>
+      <c r="C39" s="48"/>
+      <c r="E39" s="48" t="s">
+        <v>55</v>
+      </c>
+      <c r="F39" s="48"/>
+      <c r="G39" s="48"/>
+    </row>
+    <row r="40" ht="12" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="49" t="s">
+        <v>56</v>
+      </c>
+      <c r="B40" s="49"/>
+      <c r="C40" s="49"/>
+      <c r="E40" s="49" t="s">
+        <v>57</v>
+      </c>
+      <c r="F40" s="49"/>
+      <c r="G40" s="49"/>
+    </row>
   </sheetData>
-  <mergeCells count="45">
+  <mergeCells count="39">
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="D2:G2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="D3:G3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="D4:G4"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:G6"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="A6:G6"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="D7:G7"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:G8"/>
+    <mergeCell ref="A10:G10"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="D11:E11"/>
     <mergeCell ref="F11:G11"/>
-    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="E30:F30"/>
     <mergeCell ref="E31:F31"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:G33"/>
     <mergeCell ref="A35:G35"/>
     <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A37:G37"/>
-    <mergeCell ref="A38:G38"/>
-    <mergeCell ref="A39:G39"/>
-    <mergeCell ref="A40:G40"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="E42:G42"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="E43:G43"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="E44:G44"/>
-    <mergeCell ref="A47:G47"/>
-    <mergeCell ref="A48:G48"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="E49:G49"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="E50:G50"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="E52:G52"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="E53:G53"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="E38:G38"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="E39:G39"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="E40:G40"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.35" bottom="0.45" header="0.2" footer="0.25"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
-    <oddFooter>&amp;L&amp;7&amp;K475569ACR Networks &amp; Solutions, SRL · RNC 1-32-12345-6&amp;C&amp;7&amp;K94A3B8Documento offline · https://acrnetworks.do&amp;R&amp;7&amp;K94A3B8Página &amp;P de &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;7&amp;K475569ACR Networks &amp; Solutions, SRL · RNC 1-32-12345-6&amp;C&amp;7&amp;K94A3B8Documento Electrónico Verificable · https://acrnetworks.do&amp;R&amp;7&amp;K94A3B8Página &amp;P de &amp;N</oddFooter>
   </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Plantilla_Cotizacion_Manual_RA.xlsx
+++ b/Plantilla_Cotizacion_Manual_RA.xlsx
@@ -6,17 +6,38 @@
   <sheets>
     <sheet sheetId="1" name="Cotización" state="visible" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Cotización'!$A1:$F45</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Cotización'!$16:$16</definedName>
+  </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
   <si>
     <t>ACR Networks &amp; Solutions, SRL</t>
   </si>
   <si>
-    <t>[{"text":"RNC  ","font":{"name":"Calibri","size":8,"bold":true,"color":{"argb":"FF94A3B8"}}},{"text":"1-32-12345-6","font":{"name":"Calibri","size":10,"bold":true,"color":{"argb":"FF0F172A"}}}]</t>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF94A3B8"/>
+        <sz val="8.5"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">RNC  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF0F172A"/>
+        <sz val="11"/>
+        <rFont val="Consolas"/>
+      </rPr>
+      <t>1-32-12345-6</t>
+    </r>
   </si>
   <si>
     <t>ACR NETWORKS &amp; SOLUTIONS</t>
@@ -28,13 +49,29 @@
     <t>Infraestructura de Redes · Seguridad Electrónica · Fibra Óptica</t>
   </si>
   <si>
-    <t>Tel. (809) 547-2828  ·  ventas@acrnetworks.do</t>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF94A3B8"/>
+        <sz val="8.5"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">Tel. </t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF334155"/>
+        <sz val="9"/>
+        <rFont val="Consolas"/>
+      </rPr>
+      <t>(809) 547-2828</t>
+    </r>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://acrnetworks.do</t>
+    <t>ventas@acrnetworks.do   ·   https://acrnetworks.do</t>
   </si>
   <si>
     <t>COTIZACIÓN</t>
@@ -43,40 +80,122 @@
     <t>COT-2026-0521-001</t>
   </si>
   <si>
-    <t>Documento Electrónico Verificable</t>
-  </si>
-  <si>
-    <t>[{"text":"Emisión: ","font":{"name":"Calibri","size":8,"color":{"argb":"FF94A3B8"},"bold":true}},{"text":"2026-05-22","font":{"name":"Calibri","size":8.5,"color":{"argb":"FF0F172A"},"bold":true}},{"text":"   ·   Válida hasta: ","font":{"name":"Calibri","size":8,"color":{"argb":"FF94A3B8"},"bold":true}},{"text":"2026-06-21","font":{"name":"Calibri","size":8.5,"color":{"argb":"FF0F172A"},"bold":true}}]</t>
-  </si>
-  <si>
-    <t>CLIENTE</t>
-  </si>
-  <si>
-    <t>Razón Social</t>
-  </si>
-  <si>
-    <t>RNC / Contacto</t>
-  </si>
-  <si>
-    <t>Dirección</t>
-  </si>
-  <si>
-    <t>TechSolutions Caribe, SRL</t>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF1E40AF"/>
+        <sz val="8.5"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">◆ EMITIDA   </t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF64748B"/>
+        <sz val="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>·   Documento Electrónico Verificable</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF94A3B8"/>
+        <sz val="8.5"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">Emisión: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF0F172A"/>
+        <sz val="9"/>
+        <rFont val="Consolas"/>
+      </rPr>
+      <t>2026-05-22</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF94A3B8"/>
+        <sz val="8.5"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">   ·   Válida hasta: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF0F172A"/>
+        <sz val="9"/>
+        <rFont val="Consolas"/>
+      </rPr>
+      <t>2026-06-21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF475569"/>
+        <sz val="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">CLIENTE  </t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFE2E8F0"/>
+        <sz val="7"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>─────────────────────────────────────────────────────────────────────────────────────────────</t>
+    </r>
+  </si>
+  <si>
+    <t>RAZÓN SOCIAL</t>
+  </si>
+  <si>
+    <t>RNC</t>
+  </si>
+  <si>
+    <t>DIRECCIÓN</t>
+  </si>
+  <si>
+    <t>Plaza Comercial Bella Vista, SRL</t>
   </si>
   <si>
     <t>1-30-50128-3</t>
   </si>
   <si>
-    <t>Av. 27 de Febrero #500, Ensanche Naco, Santo Domingo, R.D.</t>
-  </si>
-  <si>
-    <t>Cliente #: CLI-2026-00128  ·  Ing. Luis Martínez</t>
-  </si>
-  <si>
-    <t>Tel. (809) 555-1234</t>
-  </si>
-  <si>
-    <t>compras@techsolutions.com.do</t>
+    <t>Av. Sarasota #45, Bella Vista, Santo Domingo, R.D.</t>
+  </si>
+  <si>
+    <t>Cliente: CLI-2026-00128  ·  Sr. Ramón Pérez · Administrador</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF94A3B8"/>
+        <sz val="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">Tel </t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF475569"/>
+        <sz val="8.5"/>
+        <rFont val="Consolas"/>
+      </rPr>
+      <t>(809) 555-0032</t>
+    </r>
+  </si>
+  <si>
+    <t>administracion@plazabellavista.do</t>
   </si>
   <si>
     <t>DETALLE DE PRODUCTOS Y SERVICIOS</t>
@@ -94,16 +213,13 @@
     <t>Cant.</t>
   </si>
   <si>
-    <t>Precio Unit. (RD$)</t>
-  </si>
-  <si>
-    <t>ITBIS (18%)</t>
-  </si>
-  <si>
-    <t>Importe (RD$)</t>
-  </si>
-  <si>
-    <t>MKT-RB5009</t>
+    <t>Precio Unit.</t>
+  </si>
+  <si>
+    <t>Importe</t>
+  </si>
+  <si>
+    <t>HIK-4MP-BUL</t>
   </si>
   <si>
     <r>
@@ -113,11 +229,11 @@
         <sz val="10"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>Router MikroTik RB5009UG+S+IN</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
+      <t>Cámara IP HIKVISION 4MP Bullet DS-2CD2143G2-I</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">
@@ -129,11 +245,11 @@
         <sz val="8.5"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>CPU 4-core ARM, 9× Gigabit, 1× SFP+ 10G, RouterOS L5</t>
-    </r>
-  </si>
-  <si>
-    <t>FO-SM-1KM</t>
+      <t>IR 30m, PoE 802.3af, lente fija 2.8mm, IP67, H.265+, audio bidireccional</t>
+    </r>
+  </si>
+  <si>
+    <t>HIK-4MP-DOM</t>
   </si>
   <si>
     <r>
@@ -143,11 +259,11 @@
         <sz val="10"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>Cable de Fibra Óptica Single-Mode 9/125µm</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
+      <t>Cámara IP HIKVISION 4MP Dome DS-2CD2143G2-IS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">
@@ -159,11 +275,11 @@
         <sz val="8.5"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>Armado, exterior, anti-roedor — rollo 1000 m</t>
-    </r>
-  </si>
-  <si>
-    <t>SC-APC-50</t>
+      <t>Anti-vandálica IK10, IR 30m, PoE, lente 2.8mm, audio in/out, micro SD slot</t>
+    </r>
+  </si>
+  <si>
+    <t>HIK-NVR-32</t>
   </si>
   <si>
     <r>
@@ -173,11 +289,11 @@
         <sz val="10"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>Conectores SC/APC Pre-pulidos</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
+      <t>NVR HIKVISION DS-7632NI-K2/32P</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">
@@ -189,11 +305,11 @@
         <sz val="8.5"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>Conector mecánico, pérdida &lt;0.3 dB</t>
-    </r>
-  </si>
-  <si>
-    <t>HIK-DS-4MP</t>
+      <t>32 canales, 32 puertos PoE+, H.265+, 2 bahías HDD, salida HDMI 4K, hasta 320Mbps</t>
+    </r>
+  </si>
+  <si>
+    <t>HDD-WD-10TB</t>
   </si>
   <si>
     <r>
@@ -203,11 +319,11 @@
         <sz val="10"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>Cámara IP HIKVISION 4MP DS-2CD2143G2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
+      <t>Disco Duro WD Purple 10TB Surveillance</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">
@@ -219,11 +335,11 @@
         <sz val="8.5"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>Bullet, IR 30m, PoE, lente 2.8mm, IP67</t>
-    </r>
-  </si>
-  <si>
-    <t>HIK-NVR16</t>
+      <t>CMR, 7200 RPM, 256MB caché, SATA III, 24/7, 1.5M horas MTBF, AllFrame AI</t>
+    </r>
+  </si>
+  <si>
+    <t>SW-POE-24</t>
   </si>
   <si>
     <r>
@@ -233,11 +349,11 @@
         <sz val="10"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>NVR HIKVISION DS-7616NI-K2/16P</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
+      <t>Switch PoE+ 24 puertos Gigabit + 2× SFP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">
@@ -249,11 +365,11 @@
         <sz val="8.5"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>16 canales, 16 puertos PoE, H.265+, 2 bahías HDD</t>
-    </r>
-  </si>
-  <si>
-    <t>HDD-WD-6TB</t>
+      <t>Total budget 400W IEEE 802.3at, Layer 2 manageable, VLAN/QoS, rack-mountable</t>
+    </r>
+  </si>
+  <si>
+    <t>PATCH-CAT6</t>
   </si>
   <si>
     <r>
@@ -263,11 +379,11 @@
         <sz val="10"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>Disco Duro WD Purple 6TB Surveillance</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
+      <t>Patch Panel 24 puertos Cat6 1U</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">
@@ -279,11 +395,11 @@
         <sz val="8.5"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>24/7, 256 MB caché, SATA III</t>
-    </r>
-  </si>
-  <si>
-    <t>UPS-APC15K</t>
+      <t>Keystone tooless, certificación EIA/TIA-568-B, organizador trasero incluido</t>
+    </r>
+  </si>
+  <si>
+    <t>UTP-CAT6-305</t>
   </si>
   <si>
     <r>
@@ -293,11 +409,11 @@
         <sz val="10"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>UPS APC Smart-UPS 1500VA Line-Interactive</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
+      <t>Cable UTP Cat6 23AWG CMR — caja 305m</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">
@@ -309,11 +425,11 @@
         <sz val="8.5"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>Salidas IEC, batería sellada, software PowerChute</t>
-    </r>
-  </si>
-  <si>
-    <t>INST-CCTV</t>
+      <t>Conductor cobre puro, certificación TIA, color azul, pull-box auto-dispensador</t>
+    </r>
+  </si>
+  <si>
+    <t>RJ45-CAT6</t>
   </si>
   <si>
     <r>
@@ -323,11 +439,11 @@
         <sz val="10"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>Servicio de Instalación y Configuración CCTV</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
+      <t>Conector RJ45 Cat6 Pass-Through — caja 100u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">
@@ -339,11 +455,134 @@
         <sz val="8.5"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>Tendido cableado UTP Cat6, configuración NVR, capacitación</t>
+      <t>Contactos chapados oro 50µ, polycarbonato, compatible Cat5e/Cat6/Cat6a</t>
+    </r>
+  </si>
+  <si>
+    <t>BRK-CAM-PV</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF0F172A"/>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Bracket pared/poste para cámara bullet</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF64748B"/>
+        <sz val="8.5"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Aluminio fundido, ajuste 360°, anti-vandalismo, cubre cableado</t>
+    </r>
+  </si>
+  <si>
+    <t>RACK-12U</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF0F172A"/>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rack de pared 12U 600×450mm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF64748B"/>
+        <sz val="8.5"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Puerta cerradura con llave, ventiladores 4× incluidos, organizadores 2×</t>
+    </r>
+  </si>
+  <si>
+    <t>UPS-APC-2K</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF0F172A"/>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>UPS APC Smart-UPS 2200VA SMT2200I-AR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF64748B"/>
+        <sz val="8.5"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Line-Interactive, 8 salidas IEC, software PowerChute, expansión batería opcional</t>
+    </r>
+  </si>
+  <si>
+    <t>INST-CCTV32</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF0F172A"/>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Servicio de Instalación y Configuración — 32 Cámaras</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF64748B"/>
+        <sz val="8.5"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Tendido cableado horizontal, montaje cámaras, terminación y certificación, configuración NVR + cuentas, integración red cliente, capacitación 4h al personal de TI</t>
     </r>
   </si>
   <si>
     <t>Subtotal</t>
+  </si>
+  <si>
+    <t>ITBIS (18%)</t>
   </si>
   <si>
     <t>Total Neto</t>
@@ -356,14 +595,21 @@
         <sz val="7.5"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">Validez
+      <t>VALIDEZ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="5"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
 </t>
     </r>
     <r>
       <rPr>
         <b/>
         <color rgb="FF0F172A"/>
-        <sz val="9"/>
+        <sz val="9.5"/>
         <rFont val="Calibri"/>
       </rPr>
       <t>30 días desde la emisión</t>
@@ -377,14 +623,21 @@
         <sz val="7.5"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">Forma de Pago
+      <t>FORMA DE PAGO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="5"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
 </t>
     </r>
     <r>
       <rPr>
         <b/>
         <color rgb="FF0F172A"/>
-        <sz val="9"/>
+        <sz val="9.5"/>
         <rFont val="Calibri"/>
       </rPr>
       <t>50% confirmación · 50% contra entrega</t>
@@ -398,14 +651,21 @@
         <sz val="7.5"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">Tiempo Entrega
+      <t>ENTREGA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="5"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
 </t>
     </r>
     <r>
       <rPr>
         <b/>
         <color rgb="FF0F172A"/>
-        <sz val="9"/>
+        <sz val="9.5"/>
         <rFont val="Calibri"/>
       </rPr>
       <t>7-10 días laborables</t>
@@ -419,24 +679,31 @@
         <sz val="7.5"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">Garantía
+      <t>GARANTÍA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="5"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
 </t>
     </r>
     <r>
       <rPr>
         <b/>
         <color rgb="FF0F172A"/>
-        <sz val="9"/>
+        <sz val="9.5"/>
         <rFont val="Calibri"/>
       </rPr>
       <t>12 meses · defectos de fábrica</t>
     </r>
   </si>
   <si>
-    <t>NOTAS DEL PROYECTO</t>
-  </si>
-  <si>
-    <t>Proyecto: Instalación de sistema CCTV de 8 cámaras IP + tendido de fibra óptica punto a punto entre las dos sedes del cliente. La instalación incluye configuración del NVR, integración con red existente del cliente y capacitación básica al personal de TI. Garantía sobre defectos de fábrica únicamente — no cubre daños por descargas eléctricas, manipulación incorrecta ni eventos atmosféricos.</t>
+    <t>NOTAS</t>
+  </si>
+  <si>
+    <t>Proyecto: Implementación de sistema de videovigilancia IP de 32 cámaras (24 bullet perimetrales + 8 dome interiores), grabación centralizada en NVR de 32 canales con redundancia de almacenamiento (20 TB efectivos), red dedicada con switch PoE+ manejable, respaldo eléctrico vía 2× UPS APC 2200VA, y rack de pared 12U para concentración de equipos. Garantía sobre defectos de fábrica únicamente — no cubre daños por descargas eléctricas, manipulación incorrecta ni eventos atmosféricos.</t>
   </si>
   <si>
     <t>ACEPTACIÓN DEL CLIENTE</t>
@@ -459,7 +726,7 @@
     <numFmt numFmtId="164" formatCode="00"/>
     <numFmt numFmtId="165" formatCode="&quot;RD$&quot; #,##0.00"/>
   </numFmts>
-  <fonts count="29" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -476,7 +743,7 @@
     <font>
       <b/>
       <color rgb="FF1E40AF"/>
-      <sz val="8.5"/>
+      <sz val="9"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -487,54 +754,81 @@
     <font>
       <i/>
       <color rgb="FF64748B"/>
-      <sz val="7.5"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <color rgb="FF64748B"/>
       <sz val="8"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <u/>
       <color rgb="FF1E40AF"/>
-      <sz val="8"/>
+      <sz val="8.5"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FF1E293B"/>
-      <sz val="16"/>
+      <sz val="17"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FF0F172A"/>
-      <sz val="15"/>
+      <sz val="16"/>
       <name val="Consolas"/>
     </font>
     <font>
+      <b/>
       <color rgb="FF64748B"/>
       <sz val="7.5"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="FF475569"/>
-      <sz val="7.5"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF64748B"/>
-      <sz val="7"/>
+      <color rgb="FF0F172A"/>
+      <sz val="12"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FF0F172A"/>
       <sz val="11"/>
+      <name val="Consolas"/>
+    </font>
+    <font>
+      <color rgb="FF1E293B"/>
+      <sz val="9.5"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF475569"/>
+      <sz val="8.5"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF475569"/>
+      <sz val="8"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF334155"/>
+      <sz val="8.5"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF94A3B8"/>
+      <sz val="8.5"/>
+      <name val="Consolas"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF1E293B"/>
+      <sz val="9"/>
+      <name val="Consolas"/>
+    </font>
+    <font>
+      <color rgb="FF0F172A"/>
+      <sz val="10"/>
+      <name val="Consolas"/>
     </font>
     <font>
       <b/>
@@ -543,58 +837,21 @@
       <name val="Consolas"/>
     </font>
     <font>
-      <color rgb="FF1E293B"/>
+      <color rgb="FFCBD5E1"/>
+      <sz val="8.5"/>
+      <name val="Consolas"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF475569"/>
       <sz val="9"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <color rgb="FF475569"/>
-      <sz val="8.5"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF334155"/>
-      <sz val="8"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <color rgb="FF94A3B8"/>
-      <sz val="8"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF1E293B"/>
-      <sz val="8.5"/>
-      <name val="Consolas"/>
-    </font>
-    <font>
-      <color rgb="FF0F172A"/>
-      <sz val="9.5"/>
-      <name val="Consolas"/>
-    </font>
-    <font>
-      <color rgb="FF334155"/>
-      <sz val="9"/>
-      <name val="Consolas"/>
-    </font>
-    <font>
       <b/>
       <color rgb="FF0F172A"/>
-      <sz val="9.5"/>
+      <sz val="10.5"/>
       <name val="Consolas"/>
-    </font>
-    <font>
-      <color rgb="FFCBD5E1"/>
-      <sz val="8"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF475569"/>
-      <sz val="8.5"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
@@ -605,23 +862,29 @@
     <font>
       <b/>
       <color rgb="FF0F172A"/>
-      <sz val="13"/>
+      <sz val="14"/>
       <name val="Consolas"/>
     </font>
     <font>
+      <b/>
+      <color rgb="FF0F172A"/>
+      <sz val="8.5"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <color rgb="FF334155"/>
+      <sz val="9.5"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF0F172A"/>
       <sz val="9"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FF0F172A"/>
+      <color rgb="FF64748B"/>
       <sz val="8"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <color rgb="FF64748B"/>
-      <sz val="7"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -666,9 +929,54 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="none"/>
+      <right style="none"/>
       <top style="thin">
+        <color rgb="FFE2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE2E8F0"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="FFE2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE2E8F0"/>
+      </right>
+      <top style="hair">
+        <color rgb="FFE2E8F0"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="FFE2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE2E8F0"/>
+      </right>
+      <top style="hair">
         <color rgb="FFE2E8F0"/>
       </top>
       <bottom style="thin">
@@ -681,43 +989,6 @@
       <right/>
       <top/>
       <bottom style="hair">
-        <color rgb="FFE2E8F0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFE2E8F0"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFE2E8F0"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFE2E8F0"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFE2E8F0"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFE2E8F0"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFE2E8F0"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFE2E8F0"/>
-      </right>
-      <top/>
-      <bottom style="thin">
         <color rgb="FFE2E8F0"/>
       </bottom>
       <diagonal/>
@@ -768,7 +1039,7 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="none"/>
       <right style="thin">
         <color rgb="FFE2E8F0"/>
       </right>
@@ -796,31 +1067,31 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="none"/>
       <right style="thin">
         <color rgb="FFE2E8F0"/>
       </right>
       <top style="thin">
         <color rgb="FFE2E8F0"/>
       </top>
-      <bottom/>
+      <bottom style="none"/>
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="none"/>
       <right style="thin">
         <color rgb="FFE2E8F0"/>
       </right>
-      <top/>
+      <top style="none"/>
       <bottom style="thin">
         <color rgb="FFE2E8F0"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
       <bottom style="thin">
         <color rgb="FF0F172A"/>
       </bottom>
@@ -830,7 +1101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -851,105 +1122,107 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="3" fontId="19" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="17" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="19" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="17" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="4" fontId="20" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="18" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="4" fontId="21" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="15" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="3" fontId="19" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="17" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="19" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="17" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="4" fontId="20" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="18" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="4" fontId="21" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="25" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="23" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -958,17 +1231,17 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -993,11 +1266,11 @@
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>5000</xdr:colOff>
+      <xdr:colOff>7500</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>18000</xdr:rowOff>
+      <xdr:rowOff>26999</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="666750" cy="666750"/>
+    <xdr:ext cx="685800" cy="685800"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="1" name="Picture 1">
@@ -1031,12 +1304,12 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor editAs="absolute">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>140000</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>25000</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="5143500" cy="1333500"/>
+    <xdr:ext cx="5524500" cy="1381125"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Picture 2">
@@ -1397,27 +1670,26 @@
     <tabColor rgb="FF1E40AF"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="44" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="15" customWidth="1"/>
+    <col min="3" max="3" width="56" customWidth="1"/>
+    <col min="4" max="4" width="8" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="4" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" ht="4" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-    </row>
-    <row r="2" ht="18" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1427,9 +1699,8 @@
         <v>1</v>
       </c>
       <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-    </row>
-    <row r="3" ht="14" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" ht="14" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
         <v>2</v>
       </c>
@@ -1439,559 +1710,578 @@
         <v>3</v>
       </c>
       <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-    </row>
-    <row r="4" ht="14" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" ht="14" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="6" t="s">
         <v>4</v>
       </c>
       <c r="C4" s="6"/>
       <c r="D4" s="6"/>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-    </row>
-    <row r="5" ht="14" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="F4" s="3"/>
+    </row>
+    <row r="5" ht="14" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>6</v>
       </c>
       <c r="C5"/>
       <c r="D5"/>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-    </row>
-    <row r="6" ht="3" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-    </row>
-    <row r="7" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
+      <c r="F5" s="7"/>
+    </row>
+    <row r="6" ht="3" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+    </row>
+    <row r="7" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="11" t="s">
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-    </row>
-    <row r="8" ht="16" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+    </row>
+    <row r="8" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="13" t="s">
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-    </row>
-    <row r="9" ht="10" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10" ht="14" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+    </row>
+    <row r="9" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" ht="16" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-    </row>
-    <row r="11" ht="14" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="15" t="s">
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+    </row>
+    <row r="11" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15" t="s">
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15" t="s">
+      <c r="E11" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G11" s="15"/>
-    </row>
-    <row r="12" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="16" t="s">
+      <c r="F11" s="14"/>
+    </row>
+    <row r="12" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="17" t="s">
+      <c r="B12" s="15"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E12" s="17"/>
-      <c r="F12" s="18" t="s">
+      <c r="E12" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="G12" s="18"/>
-    </row>
-    <row r="13" ht="16" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
+      <c r="F12" s="17"/>
+    </row>
+    <row r="13" ht="16" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
       <c r="D13" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19" t="s">
+      <c r="E13" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="G13" s="19"/>
-    </row>
-    <row r="14" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" ht="14" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="14" t="s">
+      <c r="F13" s="20"/>
+    </row>
+    <row r="14" ht="14" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" ht="16" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-    </row>
-    <row r="16" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="20" t="s">
+      <c r="B15" s="21"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
+    </row>
+    <row r="16" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="21" t="s">
+      <c r="B16" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="21" t="s">
+      <c r="C16" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="20" t="s">
+      <c r="D16" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="E16" s="22" t="s">
+      <c r="E16" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="F16" s="22" t="s">
+      <c r="F16" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="G16" s="22" t="s">
+    </row>
+    <row r="17" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="25">
+        <v>1</v>
+      </c>
+      <c r="B17" s="26" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="17" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="23">
+      <c r="C17" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" s="28">
+        <v>24</v>
+      </c>
+      <c r="E17" s="29">
+        <v>6850</v>
+      </c>
+      <c r="F17" s="30">
+        <f>D17*E17</f>
+        <v>164400</v>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="31">
+        <v>2</v>
+      </c>
+      <c r="B18" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" s="34">
+        <v>8</v>
+      </c>
+      <c r="E18" s="35">
+        <v>7450</v>
+      </c>
+      <c r="F18" s="36">
+        <f>D18*E18</f>
+        <v>59600</v>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="25">
+        <v>3</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" s="28">
         <v>1</v>
       </c>
-      <c r="B17" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="C17" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="D17" s="26">
+      <c r="E19" s="29">
+        <v>58500</v>
+      </c>
+      <c r="F19" s="30">
+        <f>D19*E19</f>
+        <v>58500</v>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="31">
+        <v>4</v>
+      </c>
+      <c r="B20" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="D20" s="34">
+        <v>2</v>
+      </c>
+      <c r="E20" s="35">
+        <v>14800</v>
+      </c>
+      <c r="F20" s="36">
+        <f>D20*E20</f>
+        <v>29600</v>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="25">
+        <v>5</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="D21" s="28">
         <v>1</v>
       </c>
-      <c r="E17" s="27">
-        <v>24500</v>
-      </c>
-      <c r="F17" s="28">
-        <f>IFERROR(D17*E17*0.18,0)</f>
-        <v>4410</v>
-      </c>
-      <c r="G17" s="29">
-        <f>IFERROR(D17*E17,0)</f>
-        <v>24500</v>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="30">
+      <c r="E21" s="29">
+        <v>28500</v>
+      </c>
+      <c r="F21" s="30">
+        <f>D21*E21</f>
+        <v>28500</v>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="31">
+        <v>6</v>
+      </c>
+      <c r="B22" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="D22" s="34">
         <v>2</v>
       </c>
-      <c r="B18" s="31" t="s">
+      <c r="E22" s="35">
+        <v>4250</v>
+      </c>
+      <c r="F22" s="36">
+        <f>D22*E22</f>
+        <v>8500</v>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="25">
+        <v>7</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="D23" s="28">
+        <v>4</v>
+      </c>
+      <c r="E23" s="29">
+        <v>5450</v>
+      </c>
+      <c r="F23" s="30">
+        <f>D23*E23</f>
+        <v>21800</v>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="31">
+        <v>8</v>
+      </c>
+      <c r="B24" s="32" t="s">
+        <v>43</v>
+      </c>
+      <c r="C24" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="D24" s="34">
+        <v>2</v>
+      </c>
+      <c r="E24" s="35">
+        <v>1850</v>
+      </c>
+      <c r="F24" s="36">
+        <f>D24*E24</f>
+        <v>3700</v>
+      </c>
+    </row>
+    <row r="25" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="25">
+        <v>9</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C25" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="D25" s="28">
         <v>32</v>
       </c>
-      <c r="C18" s="32" t="s">
-        <v>33</v>
-      </c>
-      <c r="D18" s="33">
-        <v>1500</v>
-      </c>
-      <c r="E18" s="34">
-        <v>78</v>
-      </c>
-      <c r="F18" s="35">
-        <f>IFERROR(D18*E18*0.18,0)</f>
-        <v>21060</v>
-      </c>
-      <c r="G18" s="36">
-        <f>IFERROR(D18*E18,0)</f>
-        <v>117000</v>
-      </c>
-    </row>
-    <row r="19" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="23">
-        <v>3</v>
-      </c>
-      <c r="B19" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="C19" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="D19" s="26">
+      <c r="E25" s="29">
+        <v>485</v>
+      </c>
+      <c r="F25" s="30">
+        <f>D25*E25</f>
+        <v>15520</v>
+      </c>
+    </row>
+    <row r="26" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="31">
+        <v>10</v>
+      </c>
+      <c r="B26" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="D26" s="34">
+        <v>1</v>
+      </c>
+      <c r="E26" s="35">
+        <v>18500</v>
+      </c>
+      <c r="F26" s="36">
+        <f>D26*E26</f>
+        <v>18500</v>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="25">
+        <v>11</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C27" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="E19" s="27">
-        <v>145</v>
-      </c>
-      <c r="F19" s="28">
-        <f>IFERROR(D19*E19*0.18,0)</f>
-        <v>1305</v>
-      </c>
-      <c r="G19" s="29">
-        <f>IFERROR(D19*E19,0)</f>
-        <v>7250</v>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="30">
-        <v>4</v>
-      </c>
-      <c r="B20" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="C20" s="32" t="s">
-        <v>37</v>
-      </c>
-      <c r="D20" s="33">
-        <v>8</v>
-      </c>
-      <c r="E20" s="34">
-        <v>6850</v>
-      </c>
-      <c r="F20" s="35">
-        <f>IFERROR(D20*E20*0.18,0)</f>
-        <v>9864</v>
-      </c>
-      <c r="G20" s="36">
-        <f>IFERROR(D20*E20,0)</f>
-        <v>54800</v>
-      </c>
-    </row>
-    <row r="21" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="23">
-        <v>5</v>
-      </c>
-      <c r="B21" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="C21" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="D21" s="26">
+      <c r="D27" s="28">
+        <v>2</v>
+      </c>
+      <c r="E27" s="29">
+        <v>38500</v>
+      </c>
+      <c r="F27" s="30">
+        <f>D27*E27</f>
+        <v>77000</v>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="31">
+        <v>12</v>
+      </c>
+      <c r="B28" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="C28" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="D28" s="34">
         <v>1</v>
       </c>
-      <c r="E21" s="27">
-        <v>21500</v>
-      </c>
-      <c r="F21" s="28">
-        <f>IFERROR(D21*E21*0.18,0)</f>
-        <v>3870</v>
-      </c>
-      <c r="G21" s="29">
-        <f>IFERROR(D21*E21,0)</f>
-        <v>21500</v>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="30">
-        <v>6</v>
-      </c>
-      <c r="B22" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="C22" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="D22" s="33">
-        <v>2</v>
-      </c>
-      <c r="E22" s="34">
-        <v>7950</v>
-      </c>
-      <c r="F22" s="35">
-        <f>IFERROR(D22*E22*0.18,0)</f>
-        <v>2862</v>
-      </c>
-      <c r="G22" s="36">
-        <f>IFERROR(D22*E22,0)</f>
-        <v>15900</v>
-      </c>
-    </row>
-    <row r="23" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="23">
-        <v>7</v>
-      </c>
-      <c r="B23" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="C23" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="D23" s="26">
-        <v>1</v>
-      </c>
-      <c r="E23" s="27">
-        <v>18500</v>
-      </c>
-      <c r="F23" s="28">
-        <f>IFERROR(D23*E23*0.18,0)</f>
-        <v>3330</v>
-      </c>
-      <c r="G23" s="29">
-        <f>IFERROR(D23*E23,0)</f>
-        <v>18500</v>
-      </c>
-    </row>
-    <row r="24" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="30">
-        <v>8</v>
-      </c>
-      <c r="B24" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="C24" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="D24" s="33">
-        <v>1</v>
-      </c>
-      <c r="E24" s="34">
-        <v>35000</v>
-      </c>
-      <c r="F24" s="35">
-        <f>IFERROR(D24*E24*0.18,0)</f>
-        <v>6300</v>
-      </c>
-      <c r="G24" s="36">
-        <f>IFERROR(D24*E24,0)</f>
-        <v>35000</v>
-      </c>
-    </row>
-    <row r="25" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="37">
-        <v>9</v>
-      </c>
-      <c r="B25" s="38"/>
-      <c r="C25" s="38"/>
-      <c r="D25" s="38"/>
-      <c r="E25" s="38"/>
-      <c r="F25" s="28">
-        <f>IFERROR(D25*E25*0.18,0)</f>
+      <c r="E28" s="35">
+        <v>145000</v>
+      </c>
+      <c r="F28" s="36">
+        <f>D28*E28</f>
+        <v>145000</v>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="37">
+        <v>13</v>
+      </c>
+      <c r="B29" s="38"/>
+      <c r="C29" s="38"/>
+      <c r="D29" s="39"/>
+      <c r="E29" s="40"/>
+      <c r="F29" s="30">
+        <f>IFERROR(D29*E29,0)</f>
         <v>0</v>
       </c>
-      <c r="G25" s="29">
-        <f>IFERROR(D25*E25,0)</f>
+    </row>
+    <row r="30" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="37">
+        <v>14</v>
+      </c>
+      <c r="B30" s="38"/>
+      <c r="C30" s="38"/>
+      <c r="D30" s="39"/>
+      <c r="E30" s="40"/>
+      <c r="F30" s="30">
+        <f>IFERROR(D30*E30,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="26" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="37">
-        <v>10</v>
-      </c>
-      <c r="B26" s="38"/>
-      <c r="C26" s="38"/>
-      <c r="D26" s="38"/>
-      <c r="E26" s="38"/>
-      <c r="F26" s="28">
-        <f>IFERROR(D26*E26*0.18,0)</f>
+    <row r="31" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="37">
+        <v>15</v>
+      </c>
+      <c r="B31" s="38"/>
+      <c r="C31" s="38"/>
+      <c r="D31" s="39"/>
+      <c r="E31" s="40"/>
+      <c r="F31" s="30">
+        <f>IFERROR(D31*E31,0)</f>
         <v>0</v>
       </c>
-      <c r="G26" s="29">
-        <f>IFERROR(D26*E26,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="37">
-        <v>11</v>
-      </c>
-      <c r="B27" s="38"/>
-      <c r="C27" s="38"/>
-      <c r="D27" s="38"/>
-      <c r="E27" s="38"/>
-      <c r="F27" s="28">
-        <f>IFERROR(D27*E27*0.18,0)</f>
-        <v>0</v>
-      </c>
-      <c r="G27" s="29">
-        <f>IFERROR(D27*E27,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" ht="8" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" ht="22" customHeight="1" spans="5:7" x14ac:dyDescent="0.25">
-      <c r="E29" s="39" t="s">
-        <v>46</v>
-      </c>
-      <c r="F29" s="39"/>
-      <c r="G29" s="40">
-        <f>SUM(G17:G27)</f>
-        <v>294450</v>
-      </c>
-    </row>
-    <row r="30" ht="22" customHeight="1" spans="5:7" x14ac:dyDescent="0.25">
-      <c r="E30" s="39" t="s">
-        <v>28</v>
-      </c>
-      <c r="F30" s="39"/>
-      <c r="G30" s="40">
-        <f>SUM(F17:F27)</f>
-        <v>53001</v>
-      </c>
-    </row>
-    <row r="31" ht="28" customHeight="1" spans="5:7" x14ac:dyDescent="0.25">
-      <c r="E31" s="41" t="s">
-        <v>47</v>
-      </c>
-      <c r="F31" s="41"/>
-      <c r="G31" s="42">
-        <f>G29+G30</f>
-        <v>347451</v>
-      </c>
-    </row>
-    <row r="32" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="43" t="s">
-        <v>48</v>
-      </c>
-      <c r="B33" s="43"/>
-      <c r="C33" s="44" t="s">
-        <v>49</v>
-      </c>
-      <c r="D33" s="43" t="s">
-        <v>50</v>
-      </c>
-      <c r="E33" s="43"/>
-      <c r="F33" s="43" t="s">
-        <v>51</v>
-      </c>
-      <c r="G33" s="43"/>
-    </row>
-    <row r="34" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" ht="14" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="45" t="s">
-        <v>52</v>
-      </c>
-      <c r="B35" s="45"/>
-      <c r="C35" s="45"/>
-      <c r="D35" s="45"/>
-      <c r="E35" s="45"/>
-      <c r="F35" s="45"/>
-      <c r="G35" s="45"/>
-    </row>
-    <row r="36" ht="50" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="46" t="s">
+    </row>
+    <row r="32" ht="10" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="22" customHeight="1" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D33" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="B36" s="46"/>
-      <c r="C36" s="46"/>
-      <c r="D36" s="46"/>
-      <c r="E36" s="46"/>
-      <c r="F36" s="46"/>
-      <c r="G36" s="46"/>
-    </row>
-    <row r="37" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" ht="44" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="47"/>
-      <c r="B38" s="47"/>
-      <c r="C38" s="47"/>
-      <c r="E38" s="47"/>
-      <c r="F38" s="47"/>
-      <c r="G38" s="47"/>
-    </row>
-    <row r="39" ht="14" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="48" t="s">
+      <c r="E33" s="41"/>
+      <c r="F33" s="42">
+        <f>SUM(F17:F31)</f>
+        <v>630620</v>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D34" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="B39" s="48"/>
-      <c r="C39" s="48"/>
-      <c r="E39" s="48" t="s">
+      <c r="E34" s="41"/>
+      <c r="F34" s="42">
+        <f>F33*0.18</f>
+        <v>113511.59999999999</v>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D35" s="43" t="s">
         <v>55</v>
       </c>
-      <c r="F39" s="48"/>
-      <c r="G39" s="48"/>
-    </row>
-    <row r="40" ht="12" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="49" t="s">
+      <c r="E35" s="43"/>
+      <c r="F35" s="44">
+        <f>F33+F34</f>
+        <v>744131.6</v>
+      </c>
+    </row>
+    <row r="36" ht="14" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="45" t="s">
         <v>56</v>
       </c>
-      <c r="B40" s="49"/>
-      <c r="C40" s="49"/>
-      <c r="E40" s="49" t="s">
+      <c r="B37" s="45"/>
+      <c r="C37" s="46" t="s">
         <v>57</v>
       </c>
-      <c r="F40" s="49"/>
-      <c r="G40" s="49"/>
+      <c r="D37" s="45" t="s">
+        <v>58</v>
+      </c>
+      <c r="E37" s="45"/>
+      <c r="F37" s="46" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="38" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="16" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="47" t="s">
+        <v>60</v>
+      </c>
+      <c r="B39" s="47"/>
+      <c r="C39" s="47"/>
+      <c r="D39" s="47"/>
+      <c r="E39" s="47"/>
+      <c r="F39" s="47"/>
+    </row>
+    <row r="40" ht="56" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="B40" s="48"/>
+      <c r="C40" s="48"/>
+      <c r="D40" s="48"/>
+      <c r="E40" s="48"/>
+      <c r="F40" s="48"/>
+    </row>
+    <row r="41" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="49"/>
+      <c r="B42" s="49"/>
+      <c r="C42" s="49"/>
+      <c r="D42" s="49"/>
+      <c r="E42" s="49"/>
+      <c r="F42" s="49"/>
+    </row>
+    <row r="43" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="B43" s="50"/>
+      <c r="C43" s="50"/>
+      <c r="D43" s="50" t="s">
+        <v>63</v>
+      </c>
+      <c r="E43" s="50"/>
+      <c r="F43" s="50"/>
+    </row>
+    <row r="44" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="51" t="s">
+        <v>64</v>
+      </c>
+      <c r="B44" s="51"/>
+      <c r="C44" s="51"/>
+      <c r="D44" s="51" t="s">
+        <v>65</v>
+      </c>
+      <c r="E44" s="51"/>
+      <c r="F44" s="51"/>
     </row>
   </sheetData>
-  <mergeCells count="39">
-    <mergeCell ref="A1:G1"/>
+  <mergeCells count="35">
+    <mergeCell ref="A1:F1"/>
     <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="E2:F2"/>
     <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="E3:F3"/>
     <mergeCell ref="B4:D4"/>
-    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="E4:F4"/>
     <mergeCell ref="B5:D5"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="A6:F6"/>
     <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:G7"/>
+    <mergeCell ref="D7:F7"/>
     <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D8:G8"/>
-    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="A10:F10"/>
     <mergeCell ref="A11:C11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="E11:F11"/>
     <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="E12:F12"/>
     <mergeCell ref="A13:C13"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="A15:F15"/>
     <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="A35:G35"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="E38:G38"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="E39:G39"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="E40:G40"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="D44:F44"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.4" right="0.4" top="0.35" bottom="0.45" header="0.2" footer="0.25"/>
+  <pageMargins left="0.35" right="0.35" top="0.35" bottom="0.5" header="0.2" footer="0.25"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
     <oddFooter>&amp;L&amp;7&amp;K475569ACR Networks &amp; Solutions, SRL · RNC 1-32-12345-6&amp;C&amp;7&amp;K94A3B8Documento Electrónico Verificable · https://acrnetworks.do&amp;R&amp;7&amp;K94A3B8Página &amp;P de &amp;N</oddFooter>

--- a/Plantilla_Cotizacion_Manual_RA.xlsx
+++ b/Plantilla_Cotizacion_Manual_RA.xlsx
@@ -7,7 +7,7 @@
     <sheet sheetId="1" name="Cotización" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Cotización'!$A1:$F45</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Cotización'!$A1:$F74</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Cotización'!$16:$16</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="89">
   <si>
     <t>ACR NETWORKS &amp; SOLUTIONS, S.R.L.</t>
   </si>
@@ -194,185 +194,74 @@
     <t>CCTV-DAH-HFW1839T</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF0F172A"/>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>Cámara IP Dahua 4K 8MP IPC-HFW1839T1-LED tipo bullet ColorVu 2.8mm</t>
-    </r>
+    <t>Cámara IP Dahua 4K 8MP IPC-HFW1839T1-LED tipo bullet ColorVu 2.8mm</t>
   </si>
   <si>
     <t>CCTV-DAH-NVR5232</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF0F172A"/>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>NVR Dahua 32 Canales NVR5232-EI 4K H.265+ con AI (rostros + cruce de línea)</t>
-    </r>
+    <t>NVR Dahua 32 Canales NVR5232-EI 4K H.265+ con AI (rostros + cruce de línea)</t>
   </si>
   <si>
     <t>STORAGE-WD-8TB-PURPLE</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF0F172A"/>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>Disco duro Western Digital Purple 8TB Surveillance WD84PURZ</t>
-    </r>
+    <t>Disco duro Western Digital Purple 8TB Surveillance WD84PURZ</t>
   </si>
   <si>
     <t>NET-UBQ-USW-24-POE</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF0F172A"/>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>Switch UniFi USW-24-POE 24-puerto gigabit con 16 PoE+ (250W total)</t>
-    </r>
+    <t>Switch UniFi USW-24-POE 24-puerto gigabit con 16 PoE+ (250W total)</t>
   </si>
   <si>
     <t>NET-UBQ-USW-LITE-8</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF0F172A"/>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>Switch UniFi USW-Lite-8-POE 8-puerto gigabit con 4 PoE+ (52W)</t>
-    </r>
+    <t>Switch UniFi USW-Lite-8-POE 8-puerto gigabit con 4 PoE+ (52W)</t>
   </si>
   <si>
     <t>FO-DROP-2H-1000M</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF0F172A"/>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>Bobina Fibra Óptica Drop 2 Hilos SM G657A1 1000m (interplanta entre edificios)</t>
-    </r>
+    <t>Bobina Fibra Óptica Drop 2 Hilos SM G657A1 1000m (interplanta entre edificios)</t>
   </si>
   <si>
     <t>NET-CAB-UTP6-305M</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF0F172A"/>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>Bobina Cable UTP Cat6 305m exterior (gel-filled) para tendido entre cámaras y rack</t>
-    </r>
+    <t>Bobina Cable UTP Cat6 305m exterior (gel-filled) para tendido entre cámaras y rack</t>
   </si>
   <si>
     <t>NET-RJ45-CAT6-PACK100</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF0F172A"/>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>Conectores RJ45 Cat6 blindados pack×100 con bota anti-tirón</t>
-    </r>
+    <t>Conectores RJ45 Cat6 blindados pack×100 con bota anti-tirón</t>
   </si>
   <si>
     <t>NET-RACK-12U</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF0F172A"/>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>Rack mural 12U 600mm con organizador y bandeja para NVR + switches</t>
-    </r>
+    <t>Rack mural 12U 600mm con organizador y bandeja para NVR + switches</t>
   </si>
   <si>
     <t>POWER-UPS-3KVA</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF0F172A"/>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>UPS APC SmartConnect 3000VA online con respaldo 2h al rack principal</t>
-    </r>
+    <t>UPS APC SmartConnect 3000VA online con respaldo 2h al rack principal</t>
   </si>
   <si>
     <t>SVC-INSTALACION</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF0F172A"/>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>Servicio técnico</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF64748B"/>
-        <sz val="8.5"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>instalación · configuración remota DMSS · programación AI y entrega final con planos as-built</t>
-    </r>
+    <t xml:space="preserve">Servicio técnico
+instalación · configuración remota DMSS · programación AI y entrega final con planos as-built</t>
   </si>
   <si>
     <t>SVC-CAPACITACION</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF0F172A"/>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>Capacitación 2 horas presencial al personal designado (uso de NVR, exportación de video, alertas móvil)</t>
-    </r>
+    <t>Capacitación 2 horas presencial al personal designado (uso de NVR, exportación de video, alertas móvil)</t>
   </si>
   <si>
     <t>Subtotal</t>
@@ -482,6 +371,146 @@
   <si>
     <t>Representante · ACR NETWORKS &amp; SOLUTIONS, S.R.L.</t>
   </si>
+  <si>
+    <t>ANEXO TÉCNICO</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FF475569"/>
+        <sz val="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>LEVANTAMIENTO FOTOGRÁFICO</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF64748B"/>
+        <sz val="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">   ·   COT-914502   ·   12 imágenes   ·   22/05/2026</t>
+    </r>
+  </si>
+  <si>
+    <t>CAPTURAS DE CAMPO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ FOTO ]
+CCTV-DAH-HFW1839T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ FOTO ]
+CCTV-DAH-NVR5232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ÍTEM 1.1 · CCTV-DAH-HFW1839T
+Cámara IP Dahua 4K 8MP IPC-HFW1839T1-LED tipo bullet ColorVu 2.8mm
+LUGAR: (especificar ubicación de instalación)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ÍTEM 2.1 · CCTV-DAH-NVR5232
+NVR Dahua 32 Canales NVR5232-EI 4K H.265+ con AI (rostros + cruce de línea)
+LUGAR: (especificar ubicación de instalación)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ FOTO ]
+STORAGE-WD-8TB-PURPLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ FOTO ]
+NET-UBQ-USW-24-POE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ÍTEM 3.1 · STORAGE-WD-8TB-PURPLE
+Disco duro Western Digital Purple 8TB Surveillance WD84PURZ
+LUGAR: (especificar ubicación de instalación)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ÍTEM 4.1 · NET-UBQ-USW-24-POE
+Switch UniFi USW-24-POE 24-puerto gigabit con 16 PoE+ (250W total)
+LUGAR: (especificar ubicación de instalación)</t>
+  </si>
+  <si>
+    <t>ANEXO TÉCNICO · Página 2 de 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ FOTO ]
+NET-UBQ-USW-LITE-8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ FOTO ]
+FO-DROP-2H-1000M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ÍTEM 5.1 · NET-UBQ-USW-LITE-8
+Switch UniFi USW-Lite-8-POE 8-puerto gigabit con 4 PoE+ (52W)
+LUGAR: (especificar ubicación de instalación)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ÍTEM 6.1 · FO-DROP-2H-1000M
+Bobina Fibra Óptica Drop 2 Hilos SM G657A1 1000m (interplanta entre edificios)
+LUGAR: (especificar ubicación de instalación)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ FOTO ]
+NET-CAB-UTP6-305M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ FOTO ]
+NET-RJ45-CAT6-PACK100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ÍTEM 7.1 · NET-CAB-UTP6-305M
+Bobina Cable UTP Cat6 305m exterior (gel-filled) para tendido entre cámaras y rack
+LUGAR: (especificar ubicación de instalación)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ÍTEM 8.1 · NET-RJ45-CAT6-PACK100
+Conectores RJ45 Cat6 blindados pack×100 con bota anti-tirón
+LUGAR: (especificar ubicación de instalación)</t>
+  </si>
+  <si>
+    <t>ANEXO TÉCNICO · Página 3 de 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ FOTO ]
+NET-RACK-12U</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ FOTO ]
+POWER-UPS-3KVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ÍTEM 9.1 · NET-RACK-12U
+Rack mural 12U 600mm con organizador y bandeja para NVR + switches
+LUGAR: (especificar ubicación de instalación)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ÍTEM 10.1 · POWER-UPS-3KVA
+UPS APC SmartConnect 3000VA online con respaldo 2h al rack principal
+LUGAR: (especificar ubicación de instalación)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ FOTO ]
+SVC-INSTALACION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ FOTO ]
+SVC-CAPACITACION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ÍTEM 11.1 · SVC-INSTALACION
+Servicio técnico
+instalación · configuración remota DMSS · programación AI y entrega final con planos as-built
+LUGAR: (especificar ubicación de instalación)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ÍTEM 12.1 · SVC-CAPACITACION
+Capacitación 2 horas presencial al personal designado (uso de NVR, exportación de video, alertas móvil)
+LUGAR: (especificar ubicación de instalación)</t>
+  </si>
 </sst>
 </file>
 
@@ -491,7 +520,7 @@
     <numFmt numFmtId="164" formatCode="00"/>
     <numFmt numFmtId="165" formatCode="&quot;RD$&quot; #,##0.00"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -578,6 +607,11 @@
     <font>
       <color rgb="FF0F172A"/>
       <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF0F172A"/>
+      <sz val="10"/>
       <name val="Consolas"/>
     </font>
     <font>
@@ -635,6 +669,17 @@
     <font>
       <color rgb="FF64748B"/>
       <sz val="8"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF94A3B8"/>
+      <sz val="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF334155"/>
+      <sz val="8.5"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -661,7 +706,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -836,11 +881,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="dashed">
+        <color rgb="FFCBD5E1"/>
+      </left>
+      <right style="dashed">
+        <color rgb="FFCBD5E1"/>
+      </right>
+      <top style="dashed">
+        <color rgb="FFCBD5E1"/>
+      </top>
+      <bottom style="dashed">
+        <color rgb="FFCBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -863,9 +923,6 @@
       <alignment horizontal="right" vertical="center" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -901,69 +958,90 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="3" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="4" fontId="15" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="4" fontId="16" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="164" fontId="12" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="3" fontId="14" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="15" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="14" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="4" fontId="15" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="16" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="21" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -987,9 +1065,9 @@
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>10000</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>18000</xdr:rowOff>
+      <xdr:rowOff>35999</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="952500" cy="533400"/>
     <xdr:pic>
@@ -1430,12 +1508,12 @@
     <tabColor rgb="FF1E40AF"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="54" customWidth="1"/>
+    <col min="3" max="3" width="50" customWidth="1"/>
     <col min="4" max="4" width="8" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -1449,44 +1527,40 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2"/>
+    <row r="2" ht="22" customHeight="1" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C2" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="D2" s="2"/>
       <c r="E2" s="3" t="s">
         <v>1</v>
       </c>
       <c r="F2" s="3"/>
     </row>
-    <row r="3" ht="14" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B3" s="4" t="s">
+    <row r="3" ht="14" customHeight="1" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="4"/>
       <c r="D3" s="4"/>
       <c r="E3" s="3" t="s">
         <v>3</v>
       </c>
       <c r="F3" s="3"/>
     </row>
-    <row r="4" ht="14" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="5" t="s">
+    <row r="4" ht="14" customHeight="1" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="5"/>
       <c r="D4" s="5"/>
       <c r="E4" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F4" s="3"/>
     </row>
-    <row r="5" ht="14" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
+    <row r="5" ht="14" customHeight="1" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
         <v>6</v>
       </c>
-      <c r="C5"/>
       <c r="D5"/>
       <c r="E5" s="3" t="s">
         <v>7</v>
@@ -1514,16 +1588,16 @@
       <c r="F7" s="8"/>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+      <c r="A8" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="10" t="s">
+      <c r="B8"/>
+      <c r="C8"/>
+      <c r="D8" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -1533,481 +1607,687 @@
       <c r="C9"/>
       <c r="D9"/>
       <c r="E9"/>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="10" ht="10" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="11" ht="16" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
     </row>
     <row r="12" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13" t="s">
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="E12" s="13" t="s">
+      <c r="E12" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="F12" s="13"/>
+      <c r="F12" s="12"/>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
+      <c r="A13" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="15" t="s">
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="E13" s="16" t="s">
+      <c r="E13" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="16"/>
+      <c r="F13" s="15"/>
     </row>
     <row r="14" ht="14" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="15" ht="16" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="17" t="s">
+      <c r="D16" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="E16" s="19" t="s">
+      <c r="E16" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="F16" s="19" t="s">
+      <c r="F16" s="18" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="17" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="20">
+      <c r="A17" s="19">
         <v>1</v>
       </c>
-      <c r="B17" s="21" t="s">
+      <c r="B17" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="22" t="s">
+      <c r="C17" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="D17" s="23">
+      <c r="D17" s="22">
         <v>36</v>
       </c>
-      <c r="E17" s="24">
-        <v>0</v>
-      </c>
-      <c r="F17" s="25">
+      <c r="E17" s="23">
+        <v>0</v>
+      </c>
+      <c r="F17" s="24">
         <f>D17*E17</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="26">
+      <c r="A18" s="25">
         <v>2</v>
       </c>
-      <c r="B18" s="27" t="s">
+      <c r="B18" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="C18" s="28" t="s">
+      <c r="C18" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="D18" s="29">
+      <c r="D18" s="28">
         <v>2</v>
       </c>
-      <c r="E18" s="30">
-        <v>0</v>
-      </c>
-      <c r="F18" s="31">
+      <c r="E18" s="29">
+        <v>0</v>
+      </c>
+      <c r="F18" s="30">
         <f>D18*E18</f>
         <v>0</v>
       </c>
     </row>
-    <row r="19" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="20">
+    <row r="19" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="19">
         <v>3</v>
       </c>
-      <c r="B19" s="21" t="s">
+      <c r="B19" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="22" t="s">
+      <c r="C19" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="D19" s="23">
+      <c r="D19" s="22">
         <v>4</v>
       </c>
-      <c r="E19" s="24">
-        <v>0</v>
-      </c>
-      <c r="F19" s="25">
+      <c r="E19" s="23">
+        <v>0</v>
+      </c>
+      <c r="F19" s="24">
         <f>D19*E19</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="26">
+      <c r="A20" s="25">
         <v>4</v>
       </c>
-      <c r="B20" s="27" t="s">
+      <c r="B20" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="28" t="s">
+      <c r="C20" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="D20" s="29">
+      <c r="D20" s="28">
         <v>2</v>
       </c>
-      <c r="E20" s="30">
-        <v>0</v>
-      </c>
-      <c r="F20" s="31">
+      <c r="E20" s="29">
+        <v>0</v>
+      </c>
+      <c r="F20" s="30">
         <f>D20*E20</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="20">
+      <c r="A21" s="19">
         <v>5</v>
       </c>
-      <c r="B21" s="21" t="s">
+      <c r="B21" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="22" t="s">
+      <c r="C21" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="23">
+      <c r="D21" s="22">
         <v>2</v>
       </c>
-      <c r="E21" s="24">
-        <v>0</v>
-      </c>
-      <c r="F21" s="25">
+      <c r="E21" s="23">
+        <v>0</v>
+      </c>
+      <c r="F21" s="24">
         <f>D21*E21</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="26">
+      <c r="A22" s="25">
         <v>6</v>
       </c>
-      <c r="B22" s="27" t="s">
+      <c r="B22" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="28" t="s">
+      <c r="C22" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="D22" s="29">
+      <c r="D22" s="28">
         <v>2</v>
       </c>
-      <c r="E22" s="30">
-        <v>0</v>
-      </c>
-      <c r="F22" s="31">
+      <c r="E22" s="29">
+        <v>0</v>
+      </c>
+      <c r="F22" s="30">
         <f>D22*E22</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="20">
+      <c r="A23" s="19">
         <v>7</v>
       </c>
-      <c r="B23" s="21" t="s">
+      <c r="B23" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="C23" s="22" t="s">
+      <c r="C23" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="D23" s="23">
+      <c r="D23" s="22">
         <v>6</v>
       </c>
-      <c r="E23" s="24">
-        <v>0</v>
-      </c>
-      <c r="F23" s="25">
+      <c r="E23" s="23">
+        <v>0</v>
+      </c>
+      <c r="F23" s="24">
         <f>D23*E23</f>
         <v>0</v>
       </c>
     </row>
-    <row r="24" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="26">
+    <row r="24" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="25">
         <v>8</v>
       </c>
-      <c r="B24" s="27" t="s">
+      <c r="B24" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="C24" s="28" t="s">
+      <c r="C24" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="D24" s="29">
+      <c r="D24" s="28">
         <v>2</v>
       </c>
-      <c r="E24" s="30">
-        <v>0</v>
-      </c>
-      <c r="F24" s="31">
+      <c r="E24" s="29">
+        <v>0</v>
+      </c>
+      <c r="F24" s="30">
         <f>D24*E24</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="20">
+      <c r="A25" s="19">
         <v>9</v>
       </c>
-      <c r="B25" s="21" t="s">
+      <c r="B25" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="C25" s="22" t="s">
+      <c r="C25" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="D25" s="23">
+      <c r="D25" s="22">
         <v>2</v>
       </c>
-      <c r="E25" s="24">
-        <v>0</v>
-      </c>
-      <c r="F25" s="25">
+      <c r="E25" s="23">
+        <v>0</v>
+      </c>
+      <c r="F25" s="24">
         <f>D25*E25</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="26">
+      <c r="A26" s="25">
         <v>10</v>
       </c>
-      <c r="B26" s="27" t="s">
+      <c r="B26" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="C26" s="28" t="s">
+      <c r="C26" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="D26" s="29">
+      <c r="D26" s="28">
         <v>1</v>
       </c>
-      <c r="E26" s="30">
-        <v>0</v>
-      </c>
-      <c r="F26" s="31">
+      <c r="E26" s="29">
+        <v>0</v>
+      </c>
+      <c r="F26" s="30">
         <f>D26*E26</f>
         <v>0</v>
       </c>
     </row>
-    <row r="27" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="20">
+    <row r="27" ht="42" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="19">
         <v>11</v>
       </c>
-      <c r="B27" s="21" t="s">
+      <c r="B27" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="C27" s="22" t="s">
+      <c r="C27" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="D27" s="23">
+      <c r="D27" s="22">
         <v>1</v>
       </c>
-      <c r="E27" s="24">
-        <v>0</v>
-      </c>
-      <c r="F27" s="25">
+      <c r="E27" s="23">
+        <v>0</v>
+      </c>
+      <c r="F27" s="24">
         <f>D27*E27</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="26">
+      <c r="A28" s="25">
         <v>12</v>
       </c>
-      <c r="B28" s="27" t="s">
+      <c r="B28" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="C28" s="28" t="s">
+      <c r="C28" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="D28" s="29">
+      <c r="D28" s="28">
         <v>1</v>
       </c>
-      <c r="E28" s="30">
-        <v>0</v>
-      </c>
-      <c r="F28" s="31">
+      <c r="E28" s="29">
+        <v>0</v>
+      </c>
+      <c r="F28" s="30">
         <f>D28*E28</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="32">
+      <c r="A29" s="31">
         <v>13</v>
       </c>
-      <c r="B29" s="33"/>
-      <c r="C29" s="33"/>
-      <c r="D29" s="34"/>
-      <c r="E29" s="35"/>
-      <c r="F29" s="25">
+      <c r="B29" s="20"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="32"/>
+      <c r="E29" s="33"/>
+      <c r="F29" s="24">
         <f>IFERROR(D29*E29,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="32">
+      <c r="A30" s="31">
         <v>14</v>
       </c>
-      <c r="B30" s="33"/>
-      <c r="C30" s="33"/>
-      <c r="D30" s="34"/>
-      <c r="E30" s="35"/>
-      <c r="F30" s="25">
+      <c r="B30" s="20"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="32"/>
+      <c r="E30" s="33"/>
+      <c r="F30" s="24">
         <f>IFERROR(D30*E30,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="32">
+      <c r="A31" s="31">
         <v>15</v>
       </c>
-      <c r="B31" s="33"/>
-      <c r="C31" s="33"/>
-      <c r="D31" s="34"/>
-      <c r="E31" s="35"/>
-      <c r="F31" s="25">
+      <c r="B31" s="20"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="32"/>
+      <c r="E31" s="33"/>
+      <c r="F31" s="24">
         <f>IFERROR(D31*E31,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="33" ht="22" customHeight="1" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D33" s="36" t="s">
+      <c r="D33" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="E33" s="36"/>
-      <c r="F33" s="37">
+      <c r="E33" s="34"/>
+      <c r="F33" s="35">
         <f>SUM(F17:F31)</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D34" s="36" t="s">
+      <c r="D34" s="34" t="s">
         <v>50</v>
       </c>
-      <c r="E34" s="36"/>
-      <c r="F34" s="37">
+      <c r="E34" s="34"/>
+      <c r="F34" s="35">
         <f>F33*0.18</f>
         <v>0</v>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D35" s="38" t="s">
+      <c r="D35" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="E35" s="38"/>
-      <c r="F35" s="39">
+      <c r="E35" s="36"/>
+      <c r="F35" s="37">
         <f>F33+F34</f>
         <v>0</v>
       </c>
     </row>
     <row r="36" ht="14" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="37" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="40" t="s">
+      <c r="A37" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="B37" s="40"/>
-      <c r="C37" s="40"/>
-      <c r="D37" s="40"/>
-      <c r="E37" s="40"/>
-      <c r="F37" s="40"/>
+      <c r="B37" s="38"/>
+      <c r="C37" s="38"/>
+      <c r="D37" s="38"/>
+      <c r="E37" s="38"/>
+      <c r="F37" s="38"/>
     </row>
     <row r="38" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="41" t="s">
+      <c r="A38" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="B38" s="41"/>
-      <c r="C38" s="41"/>
-      <c r="D38" s="41"/>
-      <c r="E38" s="41"/>
-      <c r="F38" s="41"/>
+      <c r="B38" s="39"/>
+      <c r="C38" s="39"/>
+      <c r="D38" s="39"/>
+      <c r="E38" s="39"/>
+      <c r="F38" s="39"/>
     </row>
     <row r="39" ht="8" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="40" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="42" t="s">
+      <c r="A40" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="B40" s="42"/>
-      <c r="C40" s="42" t="s">
+      <c r="B40" s="40"/>
+      <c r="C40" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="D40" s="42"/>
-      <c r="E40" s="42" t="s">
+      <c r="D40" s="40"/>
+      <c r="E40" s="40" t="s">
         <v>56</v>
       </c>
-      <c r="F40" s="42"/>
+      <c r="F40" s="40"/>
     </row>
     <row r="41" ht="28" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="42" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="43"/>
-      <c r="B42" s="43"/>
-      <c r="C42" s="43"/>
-      <c r="D42" s="43"/>
-      <c r="E42" s="43"/>
-      <c r="F42" s="43"/>
+      <c r="A42" s="41"/>
+      <c r="B42" s="41"/>
+      <c r="C42" s="41"/>
+      <c r="D42" s="41"/>
+      <c r="E42" s="41"/>
+      <c r="F42" s="41"/>
     </row>
     <row r="43" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="44" t="s">
+      <c r="A43" s="42" t="s">
         <v>57</v>
       </c>
-      <c r="B43" s="44"/>
-      <c r="C43" s="44"/>
-      <c r="D43" s="44" t="s">
-        <v>0</v>
-      </c>
-      <c r="E43" s="44"/>
-      <c r="F43" s="44"/>
+      <c r="B43" s="42"/>
+      <c r="C43" s="42"/>
+      <c r="D43" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="E43" s="42"/>
+      <c r="F43" s="42"/>
     </row>
     <row r="44" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="45" t="s">
+      <c r="A44" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="B44" s="45"/>
-      <c r="C44" s="45"/>
-      <c r="D44" s="45" t="s">
+      <c r="B44" s="43"/>
+      <c r="C44" s="43"/>
+      <c r="D44" s="43" t="s">
         <v>59</v>
       </c>
-      <c r="E44" s="45"/>
-      <c r="F44" s="45"/>
-    </row>
+      <c r="E44" s="43"/>
+      <c r="F44" s="43"/>
+    </row>
+    <row r="45" ht="8" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="44" t="s">
+        <v>60</v>
+      </c>
+      <c r="B46" s="44"/>
+      <c r="C46" s="44"/>
+      <c r="D46" s="44"/>
+      <c r="E46" s="44"/>
+      <c r="F46" s="44"/>
+    </row>
+    <row r="47" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="45" t="s">
+        <v>61</v>
+      </c>
+      <c r="B47" s="45"/>
+      <c r="C47" s="45"/>
+      <c r="D47" s="45"/>
+      <c r="E47" s="45"/>
+      <c r="F47" s="45"/>
+    </row>
+    <row r="48" ht="12" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="46" t="s">
+        <v>62</v>
+      </c>
+      <c r="B48" s="46"/>
+      <c r="C48" s="46"/>
+      <c r="D48" s="46"/>
+      <c r="E48" s="46"/>
+      <c r="F48" s="46"/>
+    </row>
+    <row r="49" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="100" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="47" t="s">
+        <v>63</v>
+      </c>
+      <c r="B50" s="47"/>
+      <c r="C50" s="47"/>
+      <c r="D50" s="47" t="s">
+        <v>64</v>
+      </c>
+      <c r="E50" s="47"/>
+      <c r="F50" s="47"/>
+    </row>
+    <row r="51" ht="50" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="48" t="s">
+        <v>65</v>
+      </c>
+      <c r="B51" s="48"/>
+      <c r="C51" s="48"/>
+      <c r="D51" s="48" t="s">
+        <v>66</v>
+      </c>
+      <c r="E51" s="48"/>
+      <c r="F51" s="48"/>
+    </row>
+    <row r="52" ht="10" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="100" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="B53" s="47"/>
+      <c r="C53" s="47"/>
+      <c r="D53" s="47" t="s">
+        <v>68</v>
+      </c>
+      <c r="E53" s="47"/>
+      <c r="F53" s="47"/>
+    </row>
+    <row r="54" ht="50" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="48" t="s">
+        <v>69</v>
+      </c>
+      <c r="B54" s="48"/>
+      <c r="C54" s="48"/>
+      <c r="D54" s="48" t="s">
+        <v>70</v>
+      </c>
+      <c r="E54" s="48"/>
+      <c r="F54" s="48"/>
+    </row>
+    <row r="55" ht="10" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="8" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="49" t="s">
+        <v>71</v>
+      </c>
+      <c r="B57" s="49"/>
+      <c r="C57" s="49"/>
+      <c r="D57" s="49"/>
+      <c r="E57" s="49"/>
+      <c r="F57" s="49"/>
+    </row>
+    <row r="58" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="100" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="B59" s="47"/>
+      <c r="C59" s="47"/>
+      <c r="D59" s="47" t="s">
+        <v>73</v>
+      </c>
+      <c r="E59" s="47"/>
+      <c r="F59" s="47"/>
+    </row>
+    <row r="60" ht="50" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="48" t="s">
+        <v>74</v>
+      </c>
+      <c r="B60" s="48"/>
+      <c r="C60" s="48"/>
+      <c r="D60" s="48" t="s">
+        <v>75</v>
+      </c>
+      <c r="E60" s="48"/>
+      <c r="F60" s="48"/>
+    </row>
+    <row r="61" ht="10" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="100" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="47" t="s">
+        <v>76</v>
+      </c>
+      <c r="B62" s="47"/>
+      <c r="C62" s="47"/>
+      <c r="D62" s="47" t="s">
+        <v>77</v>
+      </c>
+      <c r="E62" s="47"/>
+      <c r="F62" s="47"/>
+    </row>
+    <row r="63" ht="50" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="48" t="s">
+        <v>78</v>
+      </c>
+      <c r="B63" s="48"/>
+      <c r="C63" s="48"/>
+      <c r="D63" s="48" t="s">
+        <v>79</v>
+      </c>
+      <c r="E63" s="48"/>
+      <c r="F63" s="48"/>
+    </row>
+    <row r="64" ht="10" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="8" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B66" s="49"/>
+      <c r="C66" s="49"/>
+      <c r="D66" s="49"/>
+      <c r="E66" s="49"/>
+      <c r="F66" s="49"/>
+    </row>
+    <row r="67" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="100" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="47" t="s">
+        <v>81</v>
+      </c>
+      <c r="B68" s="47"/>
+      <c r="C68" s="47"/>
+      <c r="D68" s="47" t="s">
+        <v>82</v>
+      </c>
+      <c r="E68" s="47"/>
+      <c r="F68" s="47"/>
+    </row>
+    <row r="69" ht="50" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="B69" s="48"/>
+      <c r="C69" s="48"/>
+      <c r="D69" s="48" t="s">
+        <v>84</v>
+      </c>
+      <c r="E69" s="48"/>
+      <c r="F69" s="48"/>
+    </row>
+    <row r="70" ht="10" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="100" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="B71" s="47"/>
+      <c r="C71" s="47"/>
+      <c r="D71" s="47" t="s">
+        <v>86</v>
+      </c>
+      <c r="E71" s="47"/>
+      <c r="F71" s="47"/>
+    </row>
+    <row r="72" ht="50" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="48" t="s">
+        <v>87</v>
+      </c>
+      <c r="B72" s="48"/>
+      <c r="C72" s="48"/>
+      <c r="D72" s="48" t="s">
+        <v>88</v>
+      </c>
+      <c r="E72" s="48"/>
+      <c r="F72" s="48"/>
+    </row>
+    <row r="73" ht="10" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="35">
+  <mergeCells count="64">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="C2:D2"/>
     <mergeCell ref="E2:F2"/>
-    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="C3:D3"/>
     <mergeCell ref="E3:F3"/>
-    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="C4:D4"/>
     <mergeCell ref="E4:F4"/>
-    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="C5:D5"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="A7:C7"/>
@@ -2035,13 +2315,51 @@
     <mergeCell ref="D43:F43"/>
     <mergeCell ref="A44:C44"/>
     <mergeCell ref="D44:F44"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="D51:F51"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="D53:F53"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="D54:F54"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="D59:F59"/>
+    <mergeCell ref="A60:C60"/>
+    <mergeCell ref="D60:F60"/>
+    <mergeCell ref="A62:C62"/>
+    <mergeCell ref="D62:F62"/>
+    <mergeCell ref="A63:C63"/>
+    <mergeCell ref="D63:F63"/>
+    <mergeCell ref="A66:F66"/>
+    <mergeCell ref="A68:C68"/>
+    <mergeCell ref="D68:F68"/>
+    <mergeCell ref="A69:C69"/>
+    <mergeCell ref="D69:F69"/>
+    <mergeCell ref="A71:C71"/>
+    <mergeCell ref="D71:F71"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="D72:F72"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.35" right="0.35" top="0.35" bottom="0.5" header="0.2" footer="0.25"/>
+  <pageMargins left="0.35" right="0.35" top="0.9" bottom="0.7" header="0.3" footer="0.35"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
+    <oddHeader>&amp;L&amp;"Calibri,Bold"&amp;11&amp;K0F172AACR NETWORKS &amp; SOLUTIONS, S.R.L.&amp;"Calibri,Regular"&amp;8&amp;K475569
+RNC 133692678&amp;C&amp;"Calibri,Bold"&amp;9&amp;K1E40AFACR NETWORKS&amp;"Calibri,Italic"&amp;7&amp;K64748B
+Soluciones en Seguridad Electrónica, Redes y Soporte IT Corporativo&amp;R&amp;"Calibri,Bold"&amp;8&amp;K94A3B8TEL  &amp;"Calibri,Regular"&amp;K475569849-458-9955
+&amp;"Calibri,Bold"&amp;K94A3B8EMAIL  &amp;"Calibri,Regular"&amp;K475569acrnetworkssolutions@gmail.com</oddHeader>
     <oddFooter>&amp;L&amp;7&amp;K475569ACR NETWORKS &amp; SOLUTIONS, S.R.L. · RNC 133692678&amp;C&amp;7&amp;K94A3B8Documento Electrónico Verificable · https://acr-erp-noc.vercel.app/portal&amp;R&amp;7&amp;K94A3B8Página &amp;P de &amp;N</oddFooter>
   </headerFooter>
+  <rowBreaks count="3" manualBreakCount="3">
+    <brk id="45" max="16838" man="1"/>
+    <brk id="56" max="16838" man="1"/>
+    <brk id="65" max="16838" man="1"/>
+  </rowBreaks>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>